--- a/research/traditional_assets/database/data/denmark/denmark_tobacco.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_tobacco.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06993011203425846</v>
+        <v>0.06981136578778309</v>
       </c>
       <c r="C2">
-        <v>1750.134461266681</v>
+        <v>1734.454558056642</v>
       </c>
       <c r="D2">
-        <v>1740.444461266681</v>
+        <v>1743.672558056641</v>
       </c>
       <c r="E2">
-        <v>-847.2</v>
+        <v>-828.292</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18.908</v>
       </c>
       <c r="G2">
         <v>9.69</v>
@@ -1457,28 +1457,28 @@
         <v>216.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9510724</v>
       </c>
       <c r="N2">
-        <v>216.4</v>
+        <v>215.4489276</v>
       </c>
       <c r="O2">
-        <v>47.608</v>
+        <v>47.39876407200001</v>
       </c>
       <c r="P2">
-        <v>168.792</v>
+        <v>168.050163528</v>
       </c>
       <c r="Q2">
-        <v>230.192</v>
+        <v>229.450163528</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06993011203425846</v>
+        <v>0.07012022806846777</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5616680847221195</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>227.5326252764774</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06981136578778309</v>
+        <v>0.06969261954130772</v>
       </c>
       <c r="C3">
-        <v>1734.454558056642</v>
+        <v>1718.786651750497</v>
       </c>
       <c r="D3">
-        <v>1743.672558056641</v>
+        <v>1746.912651750497</v>
       </c>
       <c r="E3">
-        <v>-828.292</v>
+        <v>-809.384</v>
       </c>
       <c r="F3">
-        <v>18.908</v>
+        <v>37.816</v>
       </c>
       <c r="G3">
         <v>9.69</v>
@@ -1539,28 +1539,28 @@
         <v>216.4</v>
       </c>
       <c r="M3">
-        <v>0.9510724</v>
+        <v>1.9021448</v>
       </c>
       <c r="N3">
-        <v>215.4489276</v>
+        <v>214.4978552</v>
       </c>
       <c r="O3">
-        <v>47.39876407200001</v>
+        <v>47.189528144</v>
       </c>
       <c r="P3">
-        <v>168.050163528</v>
+        <v>167.308327056</v>
       </c>
       <c r="Q3">
-        <v>229.450163528</v>
+        <v>228.708327056</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07012022806846777</v>
+        <v>0.07031422402174257</v>
       </c>
       <c r="T3">
-        <v>0.5616680847221195</v>
+        <v>0.5661483607792743</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>227.5326252764774</v>
+        <v>113.7663126382387</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06969261954130772</v>
+        <v>0.06957387329483235</v>
       </c>
       <c r="C4">
-        <v>1718.786651750497</v>
+        <v>1703.130809350721</v>
       </c>
       <c r="D4">
-        <v>1746.912651750497</v>
+        <v>1750.164809350721</v>
       </c>
       <c r="E4">
-        <v>-809.384</v>
+        <v>-790.476</v>
       </c>
       <c r="F4">
-        <v>37.816</v>
+        <v>56.724</v>
       </c>
       <c r="G4">
         <v>9.69</v>
@@ -1621,28 +1621,28 @@
         <v>216.4</v>
       </c>
       <c r="M4">
-        <v>1.9021448</v>
+        <v>2.8532172</v>
       </c>
       <c r="N4">
-        <v>214.4978552</v>
+        <v>213.5467828</v>
       </c>
       <c r="O4">
-        <v>47.189528144</v>
+        <v>46.980292216</v>
       </c>
       <c r="P4">
-        <v>167.308327056</v>
+        <v>166.566490584</v>
       </c>
       <c r="Q4">
-        <v>228.708327056</v>
+        <v>227.966490584</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07031422402174257</v>
+        <v>0.07051221989157974</v>
       </c>
       <c r="T4">
-        <v>0.5661483607792743</v>
+        <v>0.57072101366235</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.7663126382387</v>
+        <v>75.84420842549248</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06957387329483235</v>
+        <v>0.06945512704835699</v>
       </c>
       <c r="C5">
-        <v>1703.130809350721</v>
+        <v>1687.487098359659</v>
       </c>
       <c r="D5">
-        <v>1750.164809350721</v>
+        <v>1753.429098359659</v>
       </c>
       <c r="E5">
-        <v>-790.476</v>
+        <v>-771.568</v>
       </c>
       <c r="F5">
-        <v>56.724</v>
+        <v>75.63200000000001</v>
       </c>
       <c r="G5">
         <v>9.69</v>
@@ -1703,28 +1703,28 @@
         <v>216.4</v>
       </c>
       <c r="M5">
-        <v>2.8532172</v>
+        <v>3.8042896</v>
       </c>
       <c r="N5">
-        <v>213.5467828</v>
+        <v>212.5957104</v>
       </c>
       <c r="O5">
-        <v>46.980292216</v>
+        <v>46.771056288</v>
       </c>
       <c r="P5">
-        <v>166.566490584</v>
+        <v>165.824654112</v>
       </c>
       <c r="Q5">
-        <v>227.966490584</v>
+        <v>227.224654112</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07051221989157974</v>
+        <v>0.07071434067537186</v>
       </c>
       <c r="T5">
-        <v>0.57072101366235</v>
+        <v>0.5753889301471563</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.84420842549248</v>
+        <v>56.88315631911934</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06945512704835699</v>
+        <v>0.06933638080188162</v>
       </c>
       <c r="C6">
-        <v>1687.487098359659</v>
+        <v>1671.855586784202</v>
       </c>
       <c r="D6">
-        <v>1753.429098359659</v>
+        <v>1756.705586784202</v>
       </c>
       <c r="E6">
-        <v>-771.568</v>
+        <v>-752.6600000000001</v>
       </c>
       <c r="F6">
-        <v>75.63200000000001</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="G6">
         <v>9.69</v>
@@ -1785,28 +1785,28 @@
         <v>216.4</v>
       </c>
       <c r="M6">
-        <v>3.8042896</v>
+        <v>4.755362</v>
       </c>
       <c r="N6">
-        <v>212.5957104</v>
+        <v>211.644638</v>
       </c>
       <c r="O6">
-        <v>46.771056288</v>
+        <v>46.56182036000001</v>
       </c>
       <c r="P6">
-        <v>165.824654112</v>
+        <v>165.08281764</v>
       </c>
       <c r="Q6">
-        <v>227.224654112</v>
+        <v>226.48281764</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07071434067537186</v>
+        <v>0.0709207166335596</v>
       </c>
       <c r="T6">
-        <v>0.5753889301471563</v>
+        <v>0.5801551185579585</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.88315631911934</v>
+        <v>45.50652505529548</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06933638080188162</v>
+        <v>0.06921763455540625</v>
       </c>
       <c r="C7">
-        <v>1671.855586784202</v>
+        <v>1656.236343140507</v>
       </c>
       <c r="D7">
-        <v>1756.705586784202</v>
+        <v>1759.994343140507</v>
       </c>
       <c r="E7">
-        <v>-752.6600000000001</v>
+        <v>-733.7520000000001</v>
       </c>
       <c r="F7">
-        <v>94.54000000000001</v>
+        <v>113.448</v>
       </c>
       <c r="G7">
         <v>9.69</v>
@@ -1867,28 +1867,28 @@
         <v>216.4</v>
       </c>
       <c r="M7">
-        <v>4.755362</v>
+        <v>5.7064344</v>
       </c>
       <c r="N7">
-        <v>211.644638</v>
+        <v>210.6935656</v>
       </c>
       <c r="O7">
-        <v>46.56182036000001</v>
+        <v>46.352584432</v>
       </c>
       <c r="P7">
-        <v>165.08281764</v>
+        <v>164.340981168</v>
       </c>
       <c r="Q7">
-        <v>226.48281764</v>
+        <v>225.740981168</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0709207166335596</v>
+        <v>0.07113148356958111</v>
       </c>
       <c r="T7">
-        <v>0.5801551185579585</v>
+        <v>0.5850227152328203</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.50652505529548</v>
+        <v>37.92210421274623</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06921763455540625</v>
+        <v>0.06909888830893088</v>
       </c>
       <c r="C8">
-        <v>1656.236343140507</v>
+        <v>1640.629436458775</v>
       </c>
       <c r="D8">
-        <v>1759.994343140507</v>
+        <v>1763.295436458775</v>
       </c>
       <c r="E8">
-        <v>-733.7520000000001</v>
+        <v>-714.8440000000001</v>
       </c>
       <c r="F8">
-        <v>113.448</v>
+        <v>132.356</v>
       </c>
       <c r="G8">
         <v>9.69</v>
@@ -1949,28 +1949,28 @@
         <v>216.4</v>
       </c>
       <c r="M8">
-        <v>5.706434399999999</v>
+        <v>6.657506799999999</v>
       </c>
       <c r="N8">
-        <v>210.6935656</v>
+        <v>209.7424932</v>
       </c>
       <c r="O8">
-        <v>46.352584432</v>
+        <v>46.143348504</v>
       </c>
       <c r="P8">
-        <v>164.340981168</v>
+        <v>163.599144696</v>
       </c>
       <c r="Q8">
-        <v>225.740981168</v>
+        <v>224.999144696</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07113148356958111</v>
+        <v>0.07134678312788266</v>
       </c>
       <c r="T8">
-        <v>0.5850227152328203</v>
+        <v>0.5899949914060663</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.92210421274623</v>
+        <v>32.50466075378249</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06909888830893089</v>
+        <v>0.06898014206245551</v>
       </c>
       <c r="C9">
-        <v>1640.629436458775</v>
+        <v>1625.03493628808</v>
       </c>
       <c r="D9">
-        <v>1763.295436458775</v>
+        <v>1766.60893628808</v>
       </c>
       <c r="E9">
-        <v>-714.8440000000001</v>
+        <v>-695.936</v>
       </c>
       <c r="F9">
-        <v>132.356</v>
+        <v>151.264</v>
       </c>
       <c r="G9">
         <v>9.69</v>
@@ -2031,28 +2031,28 @@
         <v>216.4</v>
       </c>
       <c r="M9">
-        <v>6.657506800000001</v>
+        <v>7.6085792</v>
       </c>
       <c r="N9">
-        <v>209.7424932</v>
+        <v>208.7914208</v>
       </c>
       <c r="O9">
-        <v>46.143348504</v>
+        <v>45.934112576</v>
       </c>
       <c r="P9">
-        <v>163.599144696</v>
+        <v>162.857308224</v>
       </c>
       <c r="Q9">
-        <v>224.999144696</v>
+        <v>224.257308224</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07134678312788267</v>
+        <v>0.07156676311136469</v>
       </c>
       <c r="T9">
-        <v>0.5899949914060664</v>
+        <v>0.5950753605396003</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.50466075378247</v>
+        <v>28.44157815955967</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06898014206245551</v>
+        <v>0.06886139581598015</v>
       </c>
       <c r="C10">
-        <v>1625.03493628808</v>
+        <v>1609.452912701252</v>
       </c>
       <c r="D10">
-        <v>1766.60893628808</v>
+        <v>1769.934912701252</v>
       </c>
       <c r="E10">
-        <v>-695.936</v>
+        <v>-677.028</v>
       </c>
       <c r="F10">
-        <v>151.264</v>
+        <v>170.172</v>
       </c>
       <c r="G10">
         <v>9.69</v>
@@ -2113,28 +2113,28 @@
         <v>216.4</v>
       </c>
       <c r="M10">
-        <v>7.6085792</v>
+        <v>8.559651599999999</v>
       </c>
       <c r="N10">
-        <v>208.7914208</v>
+        <v>207.8403484</v>
       </c>
       <c r="O10">
-        <v>45.934112576</v>
+        <v>45.72487664800001</v>
       </c>
       <c r="P10">
-        <v>162.857308224</v>
+        <v>162.115471752</v>
       </c>
       <c r="Q10">
-        <v>224.257308224</v>
+        <v>223.515471752</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07156676311136469</v>
+        <v>0.0717915778197584</v>
       </c>
       <c r="T10">
-        <v>0.5950753605396003</v>
+        <v>0.6002673861376076</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.44157815955967</v>
+        <v>25.28140280849749</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06886139581598015</v>
+        <v>0.06874264956950477</v>
       </c>
       <c r="C11">
-        <v>1609.452912701252</v>
+        <v>1593.88343629982</v>
       </c>
       <c r="D11">
-        <v>1769.934912701252</v>
+        <v>1773.27343629982</v>
       </c>
       <c r="E11">
-        <v>-677.028</v>
+        <v>-658.1200000000001</v>
       </c>
       <c r="F11">
-        <v>170.172</v>
+        <v>189.08</v>
       </c>
       <c r="G11">
         <v>9.69</v>
@@ -2195,28 +2195,28 @@
         <v>216.4</v>
       </c>
       <c r="M11">
-        <v>8.559651599999999</v>
+        <v>9.510723999999998</v>
       </c>
       <c r="N11">
-        <v>207.8403484</v>
+        <v>206.889276</v>
       </c>
       <c r="O11">
-        <v>45.72487664800001</v>
+        <v>45.51564072</v>
       </c>
       <c r="P11">
-        <v>162.115471752</v>
+        <v>161.37363528</v>
       </c>
       <c r="Q11">
-        <v>223.515471752</v>
+        <v>222.77363528</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0717915778197584</v>
+        <v>0.07202138841056085</v>
       </c>
       <c r="T11">
-        <v>0.6002673861376076</v>
+        <v>0.6055747900822371</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.28140280849749</v>
+        <v>22.75326252764774</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06874264956950477</v>
+        <v>0.06862390332302941</v>
       </c>
       <c r="C12">
-        <v>1593.88343629982</v>
+        <v>1578.326578219003</v>
       </c>
       <c r="D12">
-        <v>1773.27343629982</v>
+        <v>1776.624578219003</v>
       </c>
       <c r="E12">
-        <v>-658.12</v>
+        <v>-639.212</v>
       </c>
       <c r="F12">
-        <v>189.08</v>
+        <v>207.988</v>
       </c>
       <c r="G12">
         <v>9.69</v>
@@ -2277,28 +2277,28 @@
         <v>216.4</v>
       </c>
       <c r="M12">
-        <v>9.510724</v>
+        <v>10.4617964</v>
       </c>
       <c r="N12">
-        <v>206.889276</v>
+        <v>205.9382036</v>
       </c>
       <c r="O12">
-        <v>45.51564072</v>
+        <v>45.306404792</v>
       </c>
       <c r="P12">
-        <v>161.37363528</v>
+        <v>160.631798808</v>
       </c>
       <c r="Q12">
-        <v>222.77363528</v>
+        <v>222.031798808</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07202138841056085</v>
+        <v>0.07225636328430271</v>
       </c>
       <c r="T12">
-        <v>0.6055747900822371</v>
+        <v>0.6110014615312405</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.75326252764774</v>
+        <v>20.6847841160434</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06862390332302941</v>
+        <v>0.06850515707655405</v>
       </c>
       <c r="C13">
-        <v>1578.326578219003</v>
+        <v>1562.782410132767</v>
       </c>
       <c r="D13">
-        <v>1776.624578219003</v>
+        <v>1779.988410132767</v>
       </c>
       <c r="E13">
-        <v>-639.212</v>
+        <v>-620.3040000000001</v>
       </c>
       <c r="F13">
-        <v>207.988</v>
+        <v>226.896</v>
       </c>
       <c r="G13">
         <v>9.69</v>
@@ -2359,28 +2359,28 @@
         <v>216.4</v>
       </c>
       <c r="M13">
-        <v>10.4617964</v>
+        <v>11.4128688</v>
       </c>
       <c r="N13">
-        <v>205.9382036</v>
+        <v>204.9871312</v>
       </c>
       <c r="O13">
-        <v>45.306404792</v>
+        <v>45.097168864</v>
       </c>
       <c r="P13">
-        <v>160.631798808</v>
+        <v>159.889962336</v>
       </c>
       <c r="Q13">
-        <v>222.031798808</v>
+        <v>221.289962336</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07225636328430271</v>
+        <v>0.07249667849608414</v>
       </c>
       <c r="T13">
-        <v>0.6110014615312405</v>
+        <v>0.6165514664222665</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.6847841160434</v>
+        <v>18.96105210637312</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06850515707655405</v>
+        <v>0.06838641083007867</v>
       </c>
       <c r="C14">
-        <v>1562.782410132767</v>
+        <v>1547.251004258934</v>
       </c>
       <c r="D14">
-        <v>1779.988410132767</v>
+        <v>1783.365004258934</v>
       </c>
       <c r="E14">
-        <v>-620.3040000000001</v>
+        <v>-601.3960000000001</v>
       </c>
       <c r="F14">
-        <v>226.896</v>
+        <v>245.804</v>
       </c>
       <c r="G14">
         <v>9.69</v>
@@ -2441,28 +2441,28 @@
         <v>216.4</v>
       </c>
       <c r="M14">
-        <v>11.4128688</v>
+        <v>12.3639412</v>
       </c>
       <c r="N14">
-        <v>204.9871312</v>
+        <v>204.0360588</v>
       </c>
       <c r="O14">
-        <v>45.097168864</v>
+        <v>44.887932936</v>
       </c>
       <c r="P14">
-        <v>159.889962336</v>
+        <v>159.148125864</v>
       </c>
       <c r="Q14">
-        <v>221.289962336</v>
+        <v>220.548125864</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07249667849608414</v>
+        <v>0.07274251819549273</v>
       </c>
       <c r="T14">
-        <v>0.6165514664222665</v>
+        <v>0.6222290576326265</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.96105210637312</v>
+        <v>17.50250963665211</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06838641083007867</v>
+        <v>0.06826766458360331</v>
       </c>
       <c r="C15">
-        <v>1547.251004258934</v>
+        <v>1531.732433364345</v>
       </c>
       <c r="D15">
-        <v>1783.365004258934</v>
+        <v>1786.754433364345</v>
       </c>
       <c r="E15">
-        <v>-601.3960000000001</v>
+        <v>-582.4880000000001</v>
       </c>
       <c r="F15">
-        <v>245.804</v>
+        <v>264.712</v>
       </c>
       <c r="G15">
         <v>9.69</v>
@@ -2523,28 +2523,28 @@
         <v>216.4</v>
       </c>
       <c r="M15">
-        <v>12.3639412</v>
+        <v>13.3150136</v>
       </c>
       <c r="N15">
-        <v>204.0360588</v>
+        <v>203.0849864</v>
       </c>
       <c r="O15">
-        <v>44.887932936</v>
+        <v>44.678697008</v>
       </c>
       <c r="P15">
-        <v>159.148125864</v>
+        <v>158.406289392</v>
       </c>
       <c r="Q15">
-        <v>220.548125864</v>
+        <v>219.806289392</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07274251819549273</v>
+        <v>0.07299407509721315</v>
       </c>
       <c r="T15">
-        <v>0.6222290576326265</v>
+        <v>0.6280386858478787</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.50250963665211</v>
+        <v>16.25233037689124</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06826766458360331</v>
+        <v>0.06814891833712793</v>
       </c>
       <c r="C16">
-        <v>1531.732433364345</v>
+        <v>1516.226770770097</v>
       </c>
       <c r="D16">
-        <v>1786.754433364345</v>
+        <v>1790.156770770097</v>
       </c>
       <c r="E16">
-        <v>-582.4880000000001</v>
+        <v>-563.5799999999999</v>
       </c>
       <c r="F16">
-        <v>264.712</v>
+        <v>283.6200000000001</v>
       </c>
       <c r="G16">
         <v>9.69</v>
@@ -2605,28 +2605,28 @@
         <v>216.4</v>
       </c>
       <c r="M16">
-        <v>13.3150136</v>
+        <v>14.266086</v>
       </c>
       <c r="N16">
-        <v>203.0849864</v>
+        <v>202.133914</v>
       </c>
       <c r="O16">
-        <v>44.678697008</v>
+        <v>44.46946108</v>
       </c>
       <c r="P16">
-        <v>158.406289392</v>
+        <v>157.66445292</v>
       </c>
       <c r="Q16">
-        <v>219.806289392</v>
+        <v>219.06445292</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07299407509721315</v>
+        <v>0.07325155098485639</v>
       </c>
       <c r="T16">
-        <v>0.6280386858478787</v>
+        <v>0.6339850111976073</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.25233037689124</v>
+        <v>15.16884168509849</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06814891833712793</v>
+        <v>0.06803017209065257</v>
       </c>
       <c r="C17">
-        <v>1516.226770770097</v>
+        <v>1500.734090356819</v>
       </c>
       <c r="D17">
-        <v>1790.156770770097</v>
+        <v>1793.572090356819</v>
       </c>
       <c r="E17">
-        <v>-563.58</v>
+        <v>-544.672</v>
       </c>
       <c r="F17">
-        <v>283.62</v>
+        <v>302.528</v>
       </c>
       <c r="G17">
         <v>9.69</v>
@@ -2687,28 +2687,28 @@
         <v>216.4</v>
       </c>
       <c r="M17">
-        <v>14.266086</v>
+        <v>15.2171584</v>
       </c>
       <c r="N17">
-        <v>202.133914</v>
+        <v>201.1828416</v>
       </c>
       <c r="O17">
-        <v>44.46946108</v>
+        <v>44.260225152</v>
       </c>
       <c r="P17">
-        <v>157.66445292</v>
+        <v>156.922616448</v>
       </c>
       <c r="Q17">
-        <v>219.06445292</v>
+        <v>218.322616448</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07325155098485639</v>
+        <v>0.07351515725077687</v>
       </c>
       <c r="T17">
-        <v>0.6339850111976073</v>
+        <v>0.6400729157223295</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.16884168509849</v>
+        <v>14.22078907977984</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06803017209065257</v>
+        <v>0.0679114258441772</v>
       </c>
       <c r="C18">
-        <v>1500.734090356819</v>
+        <v>1485.25446657003</v>
       </c>
       <c r="D18">
-        <v>1793.572090356819</v>
+        <v>1797.00046657003</v>
       </c>
       <c r="E18">
-        <v>-544.672</v>
+        <v>-525.764</v>
       </c>
       <c r="F18">
-        <v>302.528</v>
+        <v>321.436</v>
       </c>
       <c r="G18">
         <v>9.69</v>
@@ -2769,28 +2769,28 @@
         <v>216.4</v>
       </c>
       <c r="M18">
-        <v>15.2171584</v>
+        <v>16.1682308</v>
       </c>
       <c r="N18">
-        <v>201.1828416</v>
+        <v>200.2317692</v>
       </c>
       <c r="O18">
-        <v>44.260225152</v>
+        <v>44.050989224</v>
       </c>
       <c r="P18">
-        <v>156.922616448</v>
+        <v>156.180779976</v>
       </c>
       <c r="Q18">
-        <v>218.322616448</v>
+        <v>217.580779976</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07351515725077687</v>
+        <v>0.07378511547491229</v>
       </c>
       <c r="T18">
-        <v>0.6400729157223295</v>
+        <v>0.6463075167416233</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.22078907977984</v>
+        <v>13.3842720750869</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0679114258441772</v>
+        <v>0.06800327959770182</v>
       </c>
       <c r="C19">
-        <v>1485.25446657003</v>
+        <v>1463.693369282003</v>
       </c>
       <c r="D19">
-        <v>1797.00046657003</v>
+        <v>1794.347369282003</v>
       </c>
       <c r="E19">
-        <v>-525.764</v>
+        <v>-506.856</v>
       </c>
       <c r="F19">
-        <v>321.436</v>
+        <v>340.3440000000001</v>
       </c>
       <c r="G19">
         <v>9.69</v>
@@ -2851,45 +2851,45 @@
         <v>216.4</v>
       </c>
       <c r="M19">
-        <v>16.1682308</v>
+        <v>17.6298192</v>
       </c>
       <c r="N19">
-        <v>200.2317692</v>
+        <v>198.7701808</v>
       </c>
       <c r="O19">
-        <v>44.050989224</v>
+        <v>43.729439776</v>
       </c>
       <c r="P19">
-        <v>156.180779976</v>
+        <v>155.040741024</v>
       </c>
       <c r="Q19">
-        <v>217.580779976</v>
+        <v>216.440741024</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07378511547491229</v>
+        <v>0.07406165804597784</v>
       </c>
       <c r="T19">
-        <v>0.6463075167416233</v>
+        <v>0.6526941812004121</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.3842720750869</v>
+        <v>12.27465792729173</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06800327959770183</v>
+        <v>0.06789623335122646</v>
       </c>
       <c r="C20">
-        <v>1463.693369282003</v>
+        <v>1447.878041788998</v>
       </c>
       <c r="D20">
-        <v>1794.347369282003</v>
+        <v>1797.440041788998</v>
       </c>
       <c r="E20">
-        <v>-506.8560000000001</v>
+        <v>-487.948</v>
       </c>
       <c r="F20">
-        <v>340.344</v>
+        <v>359.252</v>
       </c>
       <c r="G20">
         <v>9.69</v>
@@ -2933,28 +2933,28 @@
         <v>216.4</v>
       </c>
       <c r="M20">
-        <v>17.6298192</v>
+        <v>18.6092536</v>
       </c>
       <c r="N20">
-        <v>198.7701808</v>
+        <v>197.7907464</v>
       </c>
       <c r="O20">
-        <v>43.729439776</v>
+        <v>43.513964208</v>
       </c>
       <c r="P20">
-        <v>155.040741024</v>
+        <v>154.276782192</v>
       </c>
       <c r="Q20">
-        <v>216.440741024</v>
+        <v>215.676782192</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07406165804597784</v>
+        <v>0.07434502882867464</v>
       </c>
       <c r="T20">
-        <v>0.652694181200412</v>
+        <v>0.6592385410779363</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.27465792729173</v>
+        <v>11.62862329953954</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06789623335122646</v>
+        <v>0.0677891871047511</v>
       </c>
       <c r="C21">
-        <v>1447.878041788998</v>
+        <v>1432.073393540271</v>
       </c>
       <c r="D21">
-        <v>1797.440041788998</v>
+        <v>1800.543393540271</v>
       </c>
       <c r="E21">
-        <v>-487.948</v>
+        <v>-469.04</v>
       </c>
       <c r="F21">
-        <v>359.252</v>
+        <v>378.16</v>
       </c>
       <c r="G21">
         <v>9.69</v>
@@ -3015,28 +3015,28 @@
         <v>216.4</v>
       </c>
       <c r="M21">
-        <v>18.6092536</v>
+        <v>19.588688</v>
       </c>
       <c r="N21">
-        <v>197.7907464</v>
+        <v>196.811312</v>
       </c>
       <c r="O21">
-        <v>43.513964208</v>
+        <v>43.29848864</v>
       </c>
       <c r="P21">
-        <v>154.276782192</v>
+        <v>153.51282336</v>
       </c>
       <c r="Q21">
-        <v>215.676782192</v>
+        <v>214.91282336</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07434502882867464</v>
+        <v>0.07463548388093887</v>
       </c>
       <c r="T21">
-        <v>0.6592385410779363</v>
+        <v>0.6659465099523988</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.62862329953954</v>
+        <v>11.04719213456256</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0677891871047511</v>
+        <v>0.06768214085827573</v>
       </c>
       <c r="C22">
-        <v>1432.073393540271</v>
+        <v>1416.27947994591</v>
       </c>
       <c r="D22">
-        <v>1800.543393540271</v>
+        <v>1803.65747994591</v>
       </c>
       <c r="E22">
-        <v>-469.04</v>
+        <v>-450.132</v>
       </c>
       <c r="F22">
-        <v>378.16</v>
+        <v>397.068</v>
       </c>
       <c r="G22">
         <v>9.69</v>
@@ -3097,28 +3097,28 @@
         <v>216.4</v>
       </c>
       <c r="M22">
-        <v>19.588688</v>
+        <v>20.5681224</v>
       </c>
       <c r="N22">
-        <v>196.811312</v>
+        <v>195.8318776</v>
       </c>
       <c r="O22">
-        <v>43.29848864</v>
+        <v>43.083013072</v>
       </c>
       <c r="P22">
-        <v>153.51282336</v>
+        <v>152.748864528</v>
       </c>
       <c r="Q22">
-        <v>214.91282336</v>
+        <v>214.148864528</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07463548388093887</v>
+        <v>0.07493329222566547</v>
       </c>
       <c r="T22">
-        <v>0.6659465099523988</v>
+        <v>0.6728243008236831</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.04719213456256</v>
+        <v>10.52113536625006</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06768214085827573</v>
+        <v>0.06757509461180035</v>
       </c>
       <c r="C23">
-        <v>1416.27947994591</v>
+        <v>1400.496356800002</v>
       </c>
       <c r="D23">
-        <v>1803.65747994591</v>
+        <v>1806.782356800002</v>
       </c>
       <c r="E23">
-        <v>-450.1320000000001</v>
+        <v>-431.224</v>
       </c>
       <c r="F23">
-        <v>397.068</v>
+        <v>415.976</v>
       </c>
       <c r="G23">
         <v>9.69</v>
@@ -3179,28 +3179,28 @@
         <v>216.4</v>
       </c>
       <c r="M23">
-        <v>20.5681224</v>
+        <v>21.5475568</v>
       </c>
       <c r="N23">
-        <v>195.8318776</v>
+        <v>194.8524432</v>
       </c>
       <c r="O23">
-        <v>43.083013072</v>
+        <v>42.867537504</v>
       </c>
       <c r="P23">
-        <v>152.748864528</v>
+        <v>151.984905696</v>
       </c>
       <c r="Q23">
-        <v>214.148864528</v>
+        <v>213.384905696</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07493329222566547</v>
+        <v>0.07523873668179532</v>
       </c>
       <c r="T23">
-        <v>0.6728243008236829</v>
+        <v>0.6798784453070514</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.52113536625006</v>
+        <v>10.04290194051142</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06757509461180035</v>
+        <v>0.06777302836532499</v>
       </c>
       <c r="C24">
-        <v>1400.496356800002</v>
+        <v>1375.818778770407</v>
       </c>
       <c r="D24">
-        <v>1806.782356800002</v>
+        <v>1801.012778770407</v>
       </c>
       <c r="E24">
-        <v>-431.224</v>
+        <v>-412.316</v>
       </c>
       <c r="F24">
-        <v>415.976</v>
+        <v>434.884</v>
       </c>
       <c r="G24">
         <v>9.69</v>
@@ -3261,45 +3261,45 @@
         <v>216.4</v>
       </c>
       <c r="M24">
-        <v>21.5475568</v>
+        <v>23.266294</v>
       </c>
       <c r="N24">
-        <v>194.8524432</v>
+        <v>193.133706</v>
       </c>
       <c r="O24">
-        <v>42.867537504</v>
+        <v>42.48941532000001</v>
       </c>
       <c r="P24">
-        <v>151.984905696</v>
+        <v>150.64429068</v>
       </c>
       <c r="Q24">
-        <v>213.384905696</v>
+        <v>212.04429068</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07523873668179532</v>
+        <v>0.07555211476016233</v>
       </c>
       <c r="T24">
-        <v>0.6798784453070514</v>
+        <v>0.6871158143224555</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.04290194051142</v>
+        <v>9.301008574893793</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06777302836532499</v>
+        <v>0.06767924211884963</v>
       </c>
       <c r="C25">
-        <v>1375.818778770407</v>
+        <v>1359.63995708696</v>
       </c>
       <c r="D25">
-        <v>1801.012778770407</v>
+        <v>1803.74195708696</v>
       </c>
       <c r="E25">
-        <v>-412.316</v>
+        <v>-393.408</v>
       </c>
       <c r="F25">
-        <v>434.884</v>
+        <v>453.792</v>
       </c>
       <c r="G25">
         <v>9.69</v>
@@ -3343,28 +3343,28 @@
         <v>216.4</v>
       </c>
       <c r="M25">
-        <v>23.266294</v>
+        <v>24.277872</v>
       </c>
       <c r="N25">
-        <v>193.133706</v>
+        <v>192.122128</v>
       </c>
       <c r="O25">
-        <v>42.48941532000001</v>
+        <v>42.26686816</v>
       </c>
       <c r="P25">
-        <v>150.64429068</v>
+        <v>149.85525984</v>
       </c>
       <c r="Q25">
-        <v>212.04429068</v>
+        <v>211.25525984</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07555211476016233</v>
+        <v>0.07587373963006529</v>
       </c>
       <c r="T25">
-        <v>0.6871158143224555</v>
+        <v>0.6945436404172123</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.301008574893793</v>
+        <v>8.913466550939884</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06767924211884961</v>
+        <v>0.06758545587237424</v>
       </c>
       <c r="C26">
-        <v>1359.639957086961</v>
+        <v>1343.469419318555</v>
       </c>
       <c r="D26">
-        <v>1803.74195708696</v>
+        <v>1806.479419318555</v>
       </c>
       <c r="E26">
-        <v>-393.4080000000001</v>
+        <v>-374.5000000000001</v>
       </c>
       <c r="F26">
-        <v>453.792</v>
+        <v>472.7</v>
       </c>
       <c r="G26">
         <v>9.69</v>
@@ -3425,28 +3425,28 @@
         <v>216.4</v>
       </c>
       <c r="M26">
-        <v>24.277872</v>
+        <v>25.28945</v>
       </c>
       <c r="N26">
-        <v>192.122128</v>
+        <v>191.11055</v>
       </c>
       <c r="O26">
-        <v>42.26686816</v>
+        <v>42.044321</v>
       </c>
       <c r="P26">
-        <v>149.85525984</v>
+        <v>149.066229</v>
       </c>
       <c r="Q26">
-        <v>211.25525984</v>
+        <v>210.466229</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07587373963006529</v>
+        <v>0.07620394116316566</v>
       </c>
       <c r="T26">
-        <v>0.6945436404172123</v>
+        <v>0.7021695418744958</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.913466550939885</v>
+        <v>8.55692788890229</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06758545587237424</v>
+        <v>0.06749166962589888</v>
       </c>
       <c r="C27">
-        <v>1343.469419318555</v>
+        <v>1327.307203238953</v>
       </c>
       <c r="D27">
-        <v>1806.479419318555</v>
+        <v>1809.225203238953</v>
       </c>
       <c r="E27">
-        <v>-374.5000000000001</v>
+        <v>-355.592</v>
       </c>
       <c r="F27">
-        <v>472.7</v>
+        <v>491.608</v>
       </c>
       <c r="G27">
         <v>9.69</v>
@@ -3507,28 +3507,28 @@
         <v>216.4</v>
       </c>
       <c r="M27">
-        <v>25.28945</v>
+        <v>26.301028</v>
       </c>
       <c r="N27">
-        <v>191.11055</v>
+        <v>190.098972</v>
       </c>
       <c r="O27">
-        <v>42.044321</v>
+        <v>41.82177384</v>
       </c>
       <c r="P27">
-        <v>149.066229</v>
+        <v>148.27719816</v>
       </c>
       <c r="Q27">
-        <v>210.466229</v>
+        <v>209.67719816</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07620394116316566</v>
+        <v>0.07654306706202552</v>
       </c>
       <c r="T27">
-        <v>0.7021695418744958</v>
+        <v>0.7100015487765708</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.55692788890229</v>
+        <v>8.227815277790663</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06749166962589888</v>
+        <v>0.06739788337942351</v>
       </c>
       <c r="C28">
-        <v>1327.307203238953</v>
+        <v>1311.153346851923</v>
       </c>
       <c r="D28">
-        <v>1809.225203238953</v>
+        <v>1811.979346851923</v>
       </c>
       <c r="E28">
-        <v>-355.592</v>
+        <v>-336.684</v>
       </c>
       <c r="F28">
-        <v>491.608</v>
+        <v>510.516</v>
       </c>
       <c r="G28">
         <v>9.69</v>
@@ -3589,28 +3589,28 @@
         <v>216.4</v>
       </c>
       <c r="M28">
-        <v>26.301028</v>
+        <v>27.312606</v>
       </c>
       <c r="N28">
-        <v>190.098972</v>
+        <v>189.087394</v>
       </c>
       <c r="O28">
-        <v>41.82177384</v>
+        <v>41.59922668</v>
       </c>
       <c r="P28">
-        <v>148.27719816</v>
+        <v>147.48816732</v>
       </c>
       <c r="Q28">
-        <v>209.67719816</v>
+        <v>208.88816732</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07654306706202552</v>
+        <v>0.07689148408140206</v>
       </c>
       <c r="T28">
-        <v>0.7100015487765708</v>
+        <v>0.7180481312102096</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.227815277790663</v>
+        <v>7.923081378613232</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06739788337942351</v>
+        <v>0.06730409713294815</v>
       </c>
       <c r="C29">
-        <v>1311.153346851923</v>
+        <v>1295.007888392997</v>
       </c>
       <c r="D29">
-        <v>1811.979346851923</v>
+        <v>1814.741888392997</v>
       </c>
       <c r="E29">
-        <v>-336.684</v>
+        <v>-317.776</v>
       </c>
       <c r="F29">
-        <v>510.516</v>
+        <v>529.4240000000001</v>
       </c>
       <c r="G29">
         <v>9.69</v>
@@ -3671,28 +3671,28 @@
         <v>216.4</v>
       </c>
       <c r="M29">
-        <v>27.312606</v>
+        <v>28.32418400000001</v>
       </c>
       <c r="N29">
-        <v>189.087394</v>
+        <v>188.075816</v>
       </c>
       <c r="O29">
-        <v>41.59922668</v>
+        <v>41.37667952</v>
       </c>
       <c r="P29">
-        <v>147.48816732</v>
+        <v>146.69913648</v>
       </c>
       <c r="Q29">
-        <v>208.88816732</v>
+        <v>208.09913648</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07689148408140206</v>
+        <v>0.07724957935131686</v>
       </c>
       <c r="T29">
-        <v>0.7180481312102096</v>
+        <v>0.7263182298225606</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.923081378613232</v>
+        <v>7.6401141865199</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06730409713294815</v>
+        <v>0.06739127088647277</v>
       </c>
       <c r="C30">
-        <v>1295.007888392997</v>
+        <v>1273.531846974416</v>
       </c>
       <c r="D30">
-        <v>1814.741888392997</v>
+        <v>1812.173846974416</v>
       </c>
       <c r="E30">
-        <v>-317.776</v>
+        <v>-298.8679999999999</v>
       </c>
       <c r="F30">
-        <v>529.4240000000001</v>
+        <v>548.3320000000001</v>
       </c>
       <c r="G30">
         <v>9.69</v>
@@ -3753,45 +3753,45 @@
         <v>216.4</v>
       </c>
       <c r="M30">
-        <v>28.32418400000001</v>
+        <v>29.77442760000001</v>
       </c>
       <c r="N30">
-        <v>188.075816</v>
+        <v>186.6255724</v>
       </c>
       <c r="O30">
-        <v>41.37667952</v>
+        <v>41.057625928</v>
       </c>
       <c r="P30">
-        <v>146.69913648</v>
+        <v>145.567946472</v>
       </c>
       <c r="Q30">
-        <v>208.09913648</v>
+        <v>206.967946472</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07724957935131686</v>
+        <v>0.07761776181193347</v>
       </c>
       <c r="T30">
-        <v>0.7263182298225606</v>
+        <v>0.734821288959203</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.6401141865199</v>
+        <v>7.26798187045584</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06739127088647276</v>
+        <v>0.0673037246399974</v>
       </c>
       <c r="C31">
-        <v>1273.531846974417</v>
+        <v>1257.202877236066</v>
       </c>
       <c r="D31">
-        <v>1812.173846974417</v>
+        <v>1814.752877236066</v>
       </c>
       <c r="E31">
-        <v>-298.8680000000001</v>
+        <v>-279.96</v>
       </c>
       <c r="F31">
-        <v>548.332</v>
+        <v>567.24</v>
       </c>
       <c r="G31">
         <v>9.69</v>
@@ -3835,28 +3835,28 @@
         <v>216.4</v>
       </c>
       <c r="M31">
-        <v>29.7744276</v>
+        <v>30.801132</v>
       </c>
       <c r="N31">
-        <v>186.6255724</v>
+        <v>185.598868</v>
       </c>
       <c r="O31">
-        <v>41.057625928</v>
+        <v>40.83175096</v>
       </c>
       <c r="P31">
-        <v>145.567946472</v>
+        <v>144.76711704</v>
       </c>
       <c r="Q31">
-        <v>206.967946472</v>
+        <v>206.16711704</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07761776181193347</v>
+        <v>0.07799646377142486</v>
       </c>
       <c r="T31">
-        <v>0.734821288959203</v>
+        <v>0.7435672926426067</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.267981870455841</v>
+        <v>7.025715808107313</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0673037246399974</v>
+        <v>0.06721617839352204</v>
       </c>
       <c r="C32">
-        <v>1257.202877236066</v>
+        <v>1240.881258753399</v>
       </c>
       <c r="D32">
-        <v>1814.752877236066</v>
+        <v>1817.339258753399</v>
       </c>
       <c r="E32">
-        <v>-279.96</v>
+        <v>-261.052</v>
       </c>
       <c r="F32">
-        <v>567.24</v>
+        <v>586.148</v>
       </c>
       <c r="G32">
         <v>9.69</v>
@@ -3917,28 +3917,28 @@
         <v>216.4</v>
       </c>
       <c r="M32">
-        <v>30.801132</v>
+        <v>31.8278364</v>
       </c>
       <c r="N32">
-        <v>185.598868</v>
+        <v>184.5721636</v>
       </c>
       <c r="O32">
-        <v>40.83175096</v>
+        <v>40.605875992</v>
       </c>
       <c r="P32">
-        <v>144.76711704</v>
+        <v>143.966287608</v>
       </c>
       <c r="Q32">
-        <v>206.16711704</v>
+        <v>205.366287608</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07799646377142486</v>
+        <v>0.07838614259930729</v>
       </c>
       <c r="T32">
-        <v>0.7435672926426067</v>
+        <v>0.7525668036791525</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.025715808107313</v>
+        <v>6.799079814297399</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06721617839352204</v>
+        <v>0.06712863214704666</v>
       </c>
       <c r="C33">
-        <v>1240.881258753399</v>
+        <v>1224.567023002252</v>
       </c>
       <c r="D33">
-        <v>1817.339258753399</v>
+        <v>1819.933023002252</v>
       </c>
       <c r="E33">
-        <v>-261.052</v>
+        <v>-242.144</v>
       </c>
       <c r="F33">
-        <v>586.148</v>
+        <v>605.056</v>
       </c>
       <c r="G33">
         <v>9.69</v>
@@ -3999,28 +3999,28 @@
         <v>216.4</v>
       </c>
       <c r="M33">
-        <v>31.8278364</v>
+        <v>32.8545408</v>
       </c>
       <c r="N33">
-        <v>184.5721636</v>
+        <v>183.5454592</v>
       </c>
       <c r="O33">
-        <v>40.605875992</v>
+        <v>40.380001024</v>
       </c>
       <c r="P33">
-        <v>143.966287608</v>
+        <v>143.165458176</v>
       </c>
       <c r="Q33">
-        <v>205.366287608</v>
+        <v>204.565458176</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07838614259930729</v>
+        <v>0.07878728256918627</v>
       </c>
       <c r="T33">
-        <v>0.7525668036791525</v>
+        <v>0.7618310062167732</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.799079814297399</v>
+        <v>6.586608570100605</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06712863214704666</v>
+        <v>0.0670410859005713</v>
       </c>
       <c r="C34">
-        <v>1224.567023002252</v>
+        <v>1208.260201638409</v>
       </c>
       <c r="D34">
-        <v>1819.933023002252</v>
+        <v>1822.534201638409</v>
       </c>
       <c r="E34">
-        <v>-242.144</v>
+        <v>-223.236</v>
       </c>
       <c r="F34">
-        <v>605.056</v>
+        <v>623.9640000000001</v>
       </c>
       <c r="G34">
         <v>9.69</v>
@@ -4081,28 +4081,28 @@
         <v>216.4</v>
       </c>
       <c r="M34">
-        <v>32.8545408</v>
+        <v>33.8812452</v>
       </c>
       <c r="N34">
-        <v>183.5454592</v>
+        <v>182.5187548</v>
       </c>
       <c r="O34">
-        <v>40.380001024</v>
+        <v>40.154126056</v>
       </c>
       <c r="P34">
-        <v>143.165458176</v>
+        <v>142.364628744</v>
       </c>
       <c r="Q34">
-        <v>204.565458176</v>
+        <v>203.764628744</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07878728256918627</v>
+        <v>0.07920039686652433</v>
       </c>
       <c r="T34">
-        <v>0.7618310062167732</v>
+        <v>0.7713717521137259</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.586608570100605</v>
+        <v>6.387014371006647</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0670410859005713</v>
+        <v>0.06695353965409594</v>
       </c>
       <c r="C35">
-        <v>1208.260201638409</v>
+        <v>1191.960826498896</v>
       </c>
       <c r="D35">
-        <v>1822.534201638409</v>
+        <v>1825.142826498897</v>
       </c>
       <c r="E35">
-        <v>-223.236</v>
+        <v>-204.328</v>
       </c>
       <c r="F35">
-        <v>623.9640000000001</v>
+        <v>642.8720000000001</v>
       </c>
       <c r="G35">
         <v>9.69</v>
@@ -4163,28 +4163,28 @@
         <v>216.4</v>
       </c>
       <c r="M35">
-        <v>33.8812452</v>
+        <v>34.9079496</v>
       </c>
       <c r="N35">
-        <v>182.5187548</v>
+        <v>181.4920504</v>
       </c>
       <c r="O35">
-        <v>40.154126056</v>
+        <v>39.928251088</v>
       </c>
       <c r="P35">
-        <v>142.364628744</v>
+        <v>141.563799312</v>
       </c>
       <c r="Q35">
-        <v>203.764628744</v>
+        <v>202.963799312</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07920039686652433</v>
+        <v>0.07962602977893324</v>
       </c>
       <c r="T35">
-        <v>0.7713717521137259</v>
+        <v>0.7812016115227075</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.387014371006647</v>
+        <v>6.199161007153511</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06695353965409594</v>
+        <v>0.06713899340762056</v>
       </c>
       <c r="C36">
-        <v>1191.960826498896</v>
+        <v>1167.535659986119</v>
       </c>
       <c r="D36">
-        <v>1825.142826498897</v>
+        <v>1819.625659986119</v>
       </c>
       <c r="E36">
-        <v>-204.328</v>
+        <v>-185.42</v>
       </c>
       <c r="F36">
-        <v>642.8720000000001</v>
+        <v>661.7800000000001</v>
       </c>
       <c r="G36">
         <v>9.69</v>
@@ -4245,45 +4245,45 @@
         <v>216.4</v>
       </c>
       <c r="M36">
-        <v>34.9079496</v>
+        <v>36.59643400000001</v>
       </c>
       <c r="N36">
-        <v>181.4920504</v>
+        <v>179.803566</v>
       </c>
       <c r="O36">
-        <v>39.928251088</v>
+        <v>39.55678452</v>
       </c>
       <c r="P36">
-        <v>141.563799312</v>
+        <v>140.24678148</v>
       </c>
       <c r="Q36">
-        <v>202.963799312</v>
+        <v>201.64678148</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07962602977893324</v>
+        <v>0.08006475908864702</v>
       </c>
       <c r="T36">
-        <v>0.7812016115227075</v>
+        <v>0.7913339281442731</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.199161007153511</v>
+        <v>5.913144433689904</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06713899340762056</v>
+        <v>0.06705924716114518</v>
       </c>
       <c r="C37">
-        <v>1167.535659986119</v>
+        <v>1150.99598224574</v>
       </c>
       <c r="D37">
-        <v>1819.625659986119</v>
+        <v>1821.99398224574</v>
       </c>
       <c r="E37">
-        <v>-185.42</v>
+        <v>-166.5119999999999</v>
       </c>
       <c r="F37">
-        <v>661.7800000000001</v>
+        <v>680.6880000000001</v>
       </c>
       <c r="G37">
         <v>9.69</v>
@@ -4327,28 +4327,28 @@
         <v>216.4</v>
       </c>
       <c r="M37">
-        <v>36.59643400000001</v>
+        <v>37.64204640000001</v>
       </c>
       <c r="N37">
-        <v>179.803566</v>
+        <v>178.7579536</v>
       </c>
       <c r="O37">
-        <v>39.55678452</v>
+        <v>39.326749792</v>
       </c>
       <c r="P37">
-        <v>140.24678148</v>
+        <v>139.431203808</v>
       </c>
       <c r="Q37">
-        <v>201.64678148</v>
+        <v>200.831203808</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08006475908864702</v>
+        <v>0.08051719868928936</v>
       </c>
       <c r="T37">
-        <v>0.7913339281442731</v>
+        <v>0.8017828796602626</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.913144433689904</v>
+        <v>5.748890421642963</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0670592471611452</v>
+        <v>0.06697950091466982</v>
       </c>
       <c r="C38">
-        <v>1150.99598224574</v>
+        <v>1134.462477489461</v>
       </c>
       <c r="D38">
-        <v>1821.99398224574</v>
+        <v>1824.368477489461</v>
       </c>
       <c r="E38">
-        <v>-166.5120000000001</v>
+        <v>-147.604</v>
       </c>
       <c r="F38">
-        <v>680.688</v>
+        <v>699.596</v>
       </c>
       <c r="G38">
         <v>9.69</v>
@@ -4409,28 +4409,28 @@
         <v>216.4</v>
       </c>
       <c r="M38">
-        <v>37.6420464</v>
+        <v>38.6876588</v>
       </c>
       <c r="N38">
-        <v>178.7579536</v>
+        <v>177.7123412</v>
       </c>
       <c r="O38">
-        <v>39.326749792</v>
+        <v>39.096715064</v>
       </c>
       <c r="P38">
-        <v>139.431203808</v>
+        <v>138.615626136</v>
       </c>
       <c r="Q38">
-        <v>200.831203808</v>
+        <v>200.015626136</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08051719868928936</v>
+        <v>0.08098400145185686</v>
       </c>
       <c r="T38">
-        <v>0.8017828796602625</v>
+        <v>0.8125635439227914</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.748890421642964</v>
+        <v>5.593515004841803</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06697950091466982</v>
+        <v>0.06689975466819445</v>
       </c>
       <c r="C39">
-        <v>1134.462477489461</v>
+        <v>1117.935169883413</v>
       </c>
       <c r="D39">
-        <v>1824.368477489461</v>
+        <v>1826.749169883413</v>
       </c>
       <c r="E39">
-        <v>-147.604</v>
+        <v>-128.696</v>
       </c>
       <c r="F39">
-        <v>699.596</v>
+        <v>718.504</v>
       </c>
       <c r="G39">
         <v>9.69</v>
@@ -4491,28 +4491,28 @@
         <v>216.4</v>
       </c>
       <c r="M39">
-        <v>38.6876588</v>
+        <v>39.7332712</v>
       </c>
       <c r="N39">
-        <v>177.7123412</v>
+        <v>176.6667288</v>
       </c>
       <c r="O39">
-        <v>39.096715064</v>
+        <v>38.86668033599999</v>
       </c>
       <c r="P39">
-        <v>138.615626136</v>
+        <v>137.800048464</v>
       </c>
       <c r="Q39">
-        <v>200.015626136</v>
+        <v>199.200048464</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08098400145185686</v>
+        <v>0.08146586236805557</v>
       </c>
       <c r="T39">
-        <v>0.8125635439227914</v>
+        <v>0.8236919715486276</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.593515004841803</v>
+        <v>5.446317241556491</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06689975466819445</v>
+        <v>0.06682000842171909</v>
       </c>
       <c r="C40">
-        <v>1117.935169883413</v>
+        <v>1101.414083720034</v>
       </c>
       <c r="D40">
-        <v>1826.749169883413</v>
+        <v>1829.136083720034</v>
       </c>
       <c r="E40">
-        <v>-128.696</v>
+        <v>-109.788</v>
       </c>
       <c r="F40">
-        <v>718.504</v>
+        <v>737.412</v>
       </c>
       <c r="G40">
         <v>9.69</v>
@@ -4573,28 +4573,28 @@
         <v>216.4</v>
       </c>
       <c r="M40">
-        <v>39.7332712</v>
+        <v>40.7788836</v>
       </c>
       <c r="N40">
-        <v>176.6667288</v>
+        <v>175.6211164</v>
       </c>
       <c r="O40">
-        <v>38.86668033599999</v>
+        <v>38.636645608</v>
       </c>
       <c r="P40">
-        <v>137.800048464</v>
+        <v>136.984470792</v>
       </c>
       <c r="Q40">
-        <v>199.200048464</v>
+        <v>198.384470792</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08146586236805557</v>
+        <v>0.08196352200281817</v>
       </c>
       <c r="T40">
-        <v>0.8236919715486276</v>
+        <v>0.8351852656539995</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.446317241556491</v>
+        <v>5.306668081516582</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06682000842171909</v>
+        <v>0.06674026217524373</v>
       </c>
       <c r="C41">
-        <v>1101.414083720034</v>
+        <v>1084.899243418895</v>
       </c>
       <c r="D41">
-        <v>1829.136083720034</v>
+        <v>1831.529243418895</v>
       </c>
       <c r="E41">
-        <v>-109.788</v>
+        <v>-90.88</v>
       </c>
       <c r="F41">
-        <v>737.412</v>
+        <v>756.3200000000001</v>
       </c>
       <c r="G41">
         <v>9.69</v>
@@ -4655,28 +4655,28 @@
         <v>216.4</v>
       </c>
       <c r="M41">
-        <v>40.7788836</v>
+        <v>41.824496</v>
       </c>
       <c r="N41">
-        <v>175.6211164</v>
+        <v>174.575504</v>
       </c>
       <c r="O41">
-        <v>38.636645608</v>
+        <v>38.40661088</v>
       </c>
       <c r="P41">
-        <v>136.984470792</v>
+        <v>136.16889312</v>
       </c>
       <c r="Q41">
-        <v>198.384470792</v>
+        <v>197.56889312</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08196352200281817</v>
+        <v>0.08247777029207287</v>
       </c>
       <c r="T41">
-        <v>0.8351852656539995</v>
+        <v>0.8470616695628839</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.306668081516582</v>
+        <v>5.174001379478667</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06674026217524373</v>
+        <v>0.06666051592876836</v>
       </c>
       <c r="C42">
-        <v>1084.899243418895</v>
+        <v>1068.390673527532</v>
       </c>
       <c r="D42">
-        <v>1831.529243418895</v>
+        <v>1833.928673527533</v>
       </c>
       <c r="E42">
-        <v>-90.88</v>
+        <v>-71.97199999999998</v>
       </c>
       <c r="F42">
-        <v>756.3200000000001</v>
+        <v>775.2280000000001</v>
       </c>
       <c r="G42">
         <v>9.69</v>
@@ -4737,28 +4737,28 @@
         <v>216.4</v>
       </c>
       <c r="M42">
-        <v>41.824496</v>
+        <v>42.87010840000001</v>
       </c>
       <c r="N42">
-        <v>174.575504</v>
+        <v>173.5298916</v>
       </c>
       <c r="O42">
-        <v>38.40661088</v>
+        <v>38.176576152</v>
       </c>
       <c r="P42">
-        <v>136.16889312</v>
+        <v>135.353315448</v>
       </c>
       <c r="Q42">
-        <v>197.56889312</v>
+        <v>196.753315448</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08247777029207287</v>
+        <v>0.08300945072672603</v>
       </c>
       <c r="T42">
-        <v>0.8470616695628839</v>
+        <v>0.8593406634347811</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.174001379478667</v>
+        <v>5.047806223881626</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06666051592876836</v>
+        <v>0.06658076968229298</v>
       </c>
       <c r="C43">
-        <v>1068.390673527532</v>
+        <v>1051.888398722286</v>
       </c>
       <c r="D43">
-        <v>1833.928673527533</v>
+        <v>1836.334398722286</v>
       </c>
       <c r="E43">
-        <v>-71.97199999999998</v>
+        <v>-53.06399999999996</v>
       </c>
       <c r="F43">
-        <v>775.2280000000001</v>
+        <v>794.1360000000001</v>
       </c>
       <c r="G43">
         <v>9.69</v>
@@ -4819,28 +4819,28 @@
         <v>216.4</v>
       </c>
       <c r="M43">
-        <v>42.87010840000001</v>
+        <v>43.9157208</v>
       </c>
       <c r="N43">
-        <v>173.5298916</v>
+        <v>172.4842792</v>
       </c>
       <c r="O43">
-        <v>38.176576152</v>
+        <v>37.946541424</v>
       </c>
       <c r="P43">
-        <v>135.353315448</v>
+        <v>134.537737776</v>
       </c>
       <c r="Q43">
-        <v>196.753315448</v>
+        <v>195.937737776</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08300945072672603</v>
+        <v>0.08355946496947066</v>
       </c>
       <c r="T43">
-        <v>0.8593406634347811</v>
+        <v>0.872043070888468</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.047806223881626</v>
+        <v>4.927620361408255</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06658076968229298</v>
+        <v>0.06650102343581762</v>
       </c>
       <c r="C44">
-        <v>1051.888398722286</v>
+        <v>1035.392443809146</v>
       </c>
       <c r="D44">
-        <v>1836.334398722286</v>
+        <v>1838.746443809146</v>
       </c>
       <c r="E44">
-        <v>-53.06400000000008</v>
+        <v>-34.15600000000006</v>
       </c>
       <c r="F44">
-        <v>794.136</v>
+        <v>813.044</v>
       </c>
       <c r="G44">
         <v>9.69</v>
@@ -4901,28 +4901,28 @@
         <v>216.4</v>
       </c>
       <c r="M44">
-        <v>43.9157208</v>
+        <v>44.9613332</v>
       </c>
       <c r="N44">
-        <v>172.4842792</v>
+        <v>171.4386668</v>
       </c>
       <c r="O44">
-        <v>37.946541424</v>
+        <v>37.716506696</v>
       </c>
       <c r="P44">
-        <v>134.537737776</v>
+        <v>133.722160104</v>
       </c>
       <c r="Q44">
-        <v>195.937737776</v>
+        <v>195.122160104</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08355946496947066</v>
+        <v>0.08412877795757476</v>
       </c>
       <c r="T44">
-        <v>0.872043070888468</v>
+        <v>0.8851911768493017</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.927620361408255</v>
+        <v>4.813024539049923</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06650102343581762</v>
+        <v>0.06642127718934225</v>
       </c>
       <c r="C45">
-        <v>1035.392443809146</v>
+        <v>1018.902833724608</v>
       </c>
       <c r="D45">
-        <v>1838.746443809146</v>
+        <v>1841.164833724608</v>
       </c>
       <c r="E45">
-        <v>-34.15600000000006</v>
+        <v>-15.24800000000005</v>
       </c>
       <c r="F45">
-        <v>813.044</v>
+        <v>831.952</v>
       </c>
       <c r="G45">
         <v>9.69</v>
@@ -4983,28 +4983,28 @@
         <v>216.4</v>
       </c>
       <c r="M45">
-        <v>44.9613332</v>
+        <v>46.0069456</v>
       </c>
       <c r="N45">
-        <v>171.4386668</v>
+        <v>170.3930544</v>
       </c>
       <c r="O45">
-        <v>37.716506696</v>
+        <v>37.486471968</v>
       </c>
       <c r="P45">
-        <v>133.722160104</v>
+        <v>132.906582432</v>
       </c>
       <c r="Q45">
-        <v>195.122160104</v>
+        <v>194.306582432</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08412877795757476</v>
+        <v>0.08471842355239687</v>
       </c>
       <c r="T45">
-        <v>0.8851911768493017</v>
+        <v>0.8988088580230225</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.813024539049923</v>
+        <v>4.70363761770788</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06642127718934225</v>
+        <v>0.06634153094286688</v>
       </c>
       <c r="C46">
-        <v>1018.902833724608</v>
+        <v>1002.419593536528</v>
       </c>
       <c r="D46">
-        <v>1841.164833724608</v>
+        <v>1843.589593536528</v>
       </c>
       <c r="E46">
-        <v>-15.24800000000005</v>
+        <v>3.659999999999968</v>
       </c>
       <c r="F46">
-        <v>831.952</v>
+        <v>850.86</v>
       </c>
       <c r="G46">
         <v>9.69</v>
@@ -5065,28 +5065,28 @@
         <v>216.4</v>
       </c>
       <c r="M46">
-        <v>46.0069456</v>
+        <v>47.052558</v>
       </c>
       <c r="N46">
-        <v>170.3930544</v>
+        <v>169.347442</v>
       </c>
       <c r="O46">
-        <v>37.486471968</v>
+        <v>37.25643724</v>
       </c>
       <c r="P46">
-        <v>132.906582432</v>
+        <v>132.09100476</v>
       </c>
       <c r="Q46">
-        <v>194.306582432</v>
+        <v>193.49100476</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08471842355239687</v>
+        <v>0.08532951080521251</v>
       </c>
       <c r="T46">
-        <v>0.8988088580230225</v>
+        <v>0.9129217276030602</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.70363761770788</v>
+        <v>4.59911233731437</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06634153094286688</v>
+        <v>0.06715878469639151</v>
       </c>
       <c r="C47">
-        <v>1002.419593536528</v>
+        <v>958.9608470794055</v>
       </c>
       <c r="D47">
-        <v>1843.589593536528</v>
+        <v>1819.038847079406</v>
       </c>
       <c r="E47">
-        <v>3.659999999999968</v>
+        <v>22.56799999999998</v>
       </c>
       <c r="F47">
-        <v>850.86</v>
+        <v>869.768</v>
       </c>
       <c r="G47">
         <v>9.69</v>
@@ -5147,45 +5147,45 @@
         <v>216.4</v>
       </c>
       <c r="M47">
-        <v>47.052558</v>
+        <v>50.27259040000001</v>
       </c>
       <c r="N47">
-        <v>169.347442</v>
+        <v>166.1274096</v>
       </c>
       <c r="O47">
-        <v>37.25643724</v>
+        <v>36.548030112</v>
       </c>
       <c r="P47">
-        <v>132.09100476</v>
+        <v>129.579379488</v>
       </c>
       <c r="Q47">
-        <v>193.49100476</v>
+        <v>190.979379488</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08532951080521251</v>
+        <v>0.08596323091924353</v>
       </c>
       <c r="T47">
-        <v>0.9129217276030602</v>
+        <v>0.9275572960564327</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.59911233731437</v>
+        <v>4.304532515197386</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06715878469639151</v>
+        <v>0.06709853844991615</v>
       </c>
       <c r="C48">
-        <v>958.9608470794055</v>
+        <v>941.8403306080774</v>
       </c>
       <c r="D48">
-        <v>1819.038847079406</v>
+        <v>1820.826330608077</v>
       </c>
       <c r="E48">
-        <v>22.56799999999998</v>
+        <v>41.476</v>
       </c>
       <c r="F48">
-        <v>869.768</v>
+        <v>888.676</v>
       </c>
       <c r="G48">
         <v>9.69</v>
@@ -5229,28 +5229,28 @@
         <v>216.4</v>
       </c>
       <c r="M48">
-        <v>50.27259040000001</v>
+        <v>51.36547280000001</v>
       </c>
       <c r="N48">
-        <v>166.1274096</v>
+        <v>165.0345272</v>
       </c>
       <c r="O48">
-        <v>36.548030112</v>
+        <v>36.307595984</v>
       </c>
       <c r="P48">
-        <v>129.579379488</v>
+        <v>128.726931216</v>
       </c>
       <c r="Q48">
-        <v>190.979379488</v>
+        <v>190.126931216</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08596323091924353</v>
+        <v>0.08662086499984177</v>
       </c>
       <c r="T48">
-        <v>0.9275572960564327</v>
+        <v>0.9427451501118194</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.304532515197386</v>
+        <v>4.212946717001698</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06709853844991615</v>
+        <v>0.06703829220344078</v>
       </c>
       <c r="C49">
-        <v>941.8403306080774</v>
+        <v>924.723330543372</v>
       </c>
       <c r="D49">
-        <v>1820.826330608077</v>
+        <v>1822.617330543372</v>
       </c>
       <c r="E49">
-        <v>41.476</v>
+        <v>60.38400000000001</v>
       </c>
       <c r="F49">
-        <v>888.676</v>
+        <v>907.5840000000001</v>
       </c>
       <c r="G49">
         <v>9.69</v>
@@ -5311,28 +5311,28 @@
         <v>216.4</v>
       </c>
       <c r="M49">
-        <v>51.36547280000001</v>
+        <v>52.45835520000001</v>
       </c>
       <c r="N49">
-        <v>165.0345272</v>
+        <v>163.9416448</v>
       </c>
       <c r="O49">
-        <v>36.307595984</v>
+        <v>36.067161856</v>
       </c>
       <c r="P49">
-        <v>128.726931216</v>
+        <v>127.874482944</v>
       </c>
       <c r="Q49">
-        <v>190.126931216</v>
+        <v>189.274482944</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08662086499984177</v>
+        <v>0.08730379269892456</v>
       </c>
       <c r="T49">
-        <v>0.9427451501118194</v>
+        <v>0.9585171524001055</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.212946717001698</v>
+        <v>4.125176993730829</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06703829220344076</v>
+        <v>0.06697804595696541</v>
       </c>
       <c r="C50">
-        <v>924.7233305433725</v>
+        <v>907.6098572719227</v>
       </c>
       <c r="D50">
-        <v>1822.617330543372</v>
+        <v>1824.411857271923</v>
       </c>
       <c r="E50">
-        <v>60.3839999999999</v>
+        <v>79.29199999999992</v>
       </c>
       <c r="F50">
-        <v>907.5839999999999</v>
+        <v>926.492</v>
       </c>
       <c r="G50">
         <v>9.69</v>
@@ -5393,28 +5393,28 @@
         <v>216.4</v>
       </c>
       <c r="M50">
-        <v>52.4583552</v>
+        <v>53.5512376</v>
       </c>
       <c r="N50">
-        <v>163.9416448</v>
+        <v>162.8487624</v>
       </c>
       <c r="O50">
-        <v>36.067161856</v>
+        <v>35.826727728</v>
       </c>
       <c r="P50">
-        <v>127.874482944</v>
+        <v>127.022034672</v>
       </c>
       <c r="Q50">
-        <v>189.274482944</v>
+        <v>188.422034672</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08730379269892455</v>
+        <v>0.08801350187640275</v>
       </c>
       <c r="T50">
-        <v>0.9585171524001054</v>
+        <v>0.9749076645820498</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.125176993730829</v>
+        <v>4.040989708144485</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06697804595696541</v>
+        <v>0.06828279971049003</v>
       </c>
       <c r="C51">
-        <v>907.6098572719227</v>
+        <v>850.6117081855313</v>
       </c>
       <c r="D51">
-        <v>1824.411857271923</v>
+        <v>1786.321708185531</v>
       </c>
       <c r="E51">
-        <v>79.29199999999992</v>
+        <v>98.19999999999993</v>
       </c>
       <c r="F51">
-        <v>926.492</v>
+        <v>945.4</v>
       </c>
       <c r="G51">
         <v>9.69</v>
@@ -5475,45 +5475,45 @@
         <v>216.4</v>
       </c>
       <c r="M51">
-        <v>53.5512376</v>
+        <v>57.95302</v>
       </c>
       <c r="N51">
-        <v>162.8487624</v>
+        <v>158.44698</v>
       </c>
       <c r="O51">
-        <v>35.826727728</v>
+        <v>34.8583356</v>
       </c>
       <c r="P51">
-        <v>127.022034672</v>
+        <v>123.5886444</v>
       </c>
       <c r="Q51">
-        <v>188.422034672</v>
+        <v>184.9886444</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08801350187640275</v>
+        <v>0.08875159942098007</v>
       </c>
       <c r="T51">
-        <v>0.9749076645820498</v>
+        <v>0.9919537972512719</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.040989708144485</v>
+        <v>3.734059070605811</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06828279971049003</v>
+        <v>0.06824985346401467</v>
       </c>
       <c r="C52">
-        <v>850.6117081855313</v>
+        <v>832.6459358833456</v>
       </c>
       <c r="D52">
-        <v>1786.321708185531</v>
+        <v>1787.263935883346</v>
       </c>
       <c r="E52">
-        <v>98.19999999999993</v>
+        <v>117.1079999999999</v>
       </c>
       <c r="F52">
-        <v>945.4</v>
+        <v>964.308</v>
       </c>
       <c r="G52">
         <v>9.69</v>
@@ -5557,28 +5557,28 @@
         <v>216.4</v>
       </c>
       <c r="M52">
-        <v>57.95302</v>
+        <v>59.1120804</v>
       </c>
       <c r="N52">
-        <v>158.44698</v>
+        <v>157.2879196</v>
       </c>
       <c r="O52">
-        <v>34.8583356</v>
+        <v>34.603342312</v>
       </c>
       <c r="P52">
-        <v>123.5886444</v>
+        <v>122.684577288</v>
       </c>
       <c r="Q52">
-        <v>184.9886444</v>
+        <v>184.084577288</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08875159942098007</v>
+        <v>0.0895198233959483</v>
       </c>
       <c r="T52">
-        <v>0.9919537972512719</v>
+        <v>1.009695690437605</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.734059070605811</v>
+        <v>3.660842226084129</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06824985346401467</v>
+        <v>0.06821690721753929</v>
       </c>
       <c r="C53">
-        <v>832.6459358833456</v>
+        <v>814.6811580958221</v>
       </c>
       <c r="D53">
-        <v>1787.263935883346</v>
+        <v>1788.207158095822</v>
       </c>
       <c r="E53">
-        <v>117.1079999999999</v>
+        <v>136.016</v>
       </c>
       <c r="F53">
-        <v>964.308</v>
+        <v>983.216</v>
       </c>
       <c r="G53">
         <v>9.69</v>
@@ -5639,28 +5639,28 @@
         <v>216.4</v>
       </c>
       <c r="M53">
-        <v>59.1120804</v>
+        <v>60.2711408</v>
       </c>
       <c r="N53">
-        <v>157.2879196</v>
+        <v>156.1288592</v>
       </c>
       <c r="O53">
-        <v>34.603342312</v>
+        <v>34.34834902400001</v>
       </c>
       <c r="P53">
-        <v>122.684577288</v>
+        <v>121.780510176</v>
       </c>
       <c r="Q53">
-        <v>184.084577288</v>
+        <v>183.180510176</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0895198233959483</v>
+        <v>0.09032005670320686</v>
       </c>
       <c r="T53">
-        <v>1.009695690437605</v>
+        <v>1.028176829173369</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.660842226084129</v>
+        <v>3.59044141404405</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06821690721753929</v>
+        <v>0.06818396097106393</v>
       </c>
       <c r="C54">
-        <v>814.6811580958221</v>
+        <v>796.7173763983446</v>
       </c>
       <c r="D54">
-        <v>1788.207158095822</v>
+        <v>1789.151376398345</v>
       </c>
       <c r="E54">
-        <v>136.016</v>
+        <v>154.924</v>
       </c>
       <c r="F54">
-        <v>983.216</v>
+        <v>1002.124</v>
       </c>
       <c r="G54">
         <v>9.69</v>
@@ -5721,28 +5721,28 @@
         <v>216.4</v>
       </c>
       <c r="M54">
-        <v>60.2711408</v>
+        <v>61.4302012</v>
       </c>
       <c r="N54">
-        <v>156.1288592</v>
+        <v>154.9697988</v>
       </c>
       <c r="O54">
-        <v>34.34834902400001</v>
+        <v>34.093355736</v>
       </c>
       <c r="P54">
-        <v>121.780510176</v>
+        <v>120.876443064</v>
       </c>
       <c r="Q54">
-        <v>183.180510176</v>
+        <v>182.276443064</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09032005670320686</v>
+        <v>0.09115434249162538</v>
       </c>
       <c r="T54">
-        <v>1.028176829173369</v>
+        <v>1.047444399344697</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.59044141404405</v>
+        <v>3.522697236420577</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06818396097106393</v>
+        <v>0.06933037472458857</v>
       </c>
       <c r="C55">
-        <v>796.7173763983446</v>
+        <v>745.5296339570751</v>
       </c>
       <c r="D55">
-        <v>1789.151376398345</v>
+        <v>1756.871633957075</v>
       </c>
       <c r="E55">
-        <v>154.924</v>
+        <v>173.832</v>
       </c>
       <c r="F55">
-        <v>1002.124</v>
+        <v>1021.032</v>
       </c>
       <c r="G55">
         <v>9.69</v>
@@ -5803,45 +5803,45 @@
         <v>216.4</v>
       </c>
       <c r="M55">
-        <v>61.4302012</v>
+        <v>65.44815120000001</v>
       </c>
       <c r="N55">
-        <v>154.9697988</v>
+        <v>150.9518488</v>
       </c>
       <c r="O55">
-        <v>34.093355736</v>
+        <v>33.209406736</v>
       </c>
       <c r="P55">
-        <v>120.876443064</v>
+        <v>117.742442064</v>
       </c>
       <c r="Q55">
-        <v>182.276443064</v>
+        <v>179.142442064</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09115434249162538</v>
+        <v>0.09202490157519252</v>
       </c>
       <c r="T55">
-        <v>1.047444399344697</v>
+        <v>1.067549689958257</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.22</v>
       </c>
       <c r="W55">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.522697236420577</v>
+        <v>3.306434116659967</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06933037472458857</v>
+        <v>0.06931926847811319</v>
       </c>
       <c r="C56">
-        <v>745.5296339570751</v>
+        <v>726.9287657960547</v>
       </c>
       <c r="D56">
-        <v>1756.871633957075</v>
+        <v>1757.178765796055</v>
       </c>
       <c r="E56">
-        <v>173.832</v>
+        <v>192.74</v>
       </c>
       <c r="F56">
-        <v>1021.032</v>
+        <v>1039.94</v>
       </c>
       <c r="G56">
         <v>9.69</v>
@@ -5885,28 +5885,28 @@
         <v>216.4</v>
       </c>
       <c r="M56">
-        <v>65.44815120000001</v>
+        <v>66.66015400000001</v>
       </c>
       <c r="N56">
-        <v>150.9518488</v>
+        <v>149.739846</v>
       </c>
       <c r="O56">
-        <v>33.209406736</v>
+        <v>32.94276612</v>
       </c>
       <c r="P56">
-        <v>117.742442064</v>
+        <v>116.79707988</v>
       </c>
       <c r="Q56">
-        <v>179.142442064</v>
+        <v>178.19707988</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09202490157519252</v>
+        <v>0.09293415217358486</v>
       </c>
       <c r="T56">
-        <v>1.067549689958257</v>
+        <v>1.088548549043531</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.306434116659967</v>
+        <v>3.246317132720695</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06931926847811319</v>
+        <v>0.06930816223163783</v>
       </c>
       <c r="C57">
-        <v>726.9287657960547</v>
+        <v>708.3280050378264</v>
       </c>
       <c r="D57">
-        <v>1757.178765796055</v>
+        <v>1757.486005037827</v>
       </c>
       <c r="E57">
-        <v>192.74</v>
+        <v>211.6480000000001</v>
       </c>
       <c r="F57">
-        <v>1039.94</v>
+        <v>1058.848</v>
       </c>
       <c r="G57">
         <v>9.69</v>
@@ -5967,28 +5967,28 @@
         <v>216.4</v>
       </c>
       <c r="M57">
-        <v>66.66015400000001</v>
+        <v>67.87215680000001</v>
       </c>
       <c r="N57">
-        <v>149.739846</v>
+        <v>148.5278432</v>
       </c>
       <c r="O57">
-        <v>32.94276612</v>
+        <v>32.67612550400001</v>
       </c>
       <c r="P57">
-        <v>116.79707988</v>
+        <v>115.851717696</v>
       </c>
       <c r="Q57">
-        <v>178.19707988</v>
+        <v>177.251717696</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09293415217358486</v>
+        <v>0.09388473234463141</v>
       </c>
       <c r="T57">
-        <v>1.088548549043531</v>
+        <v>1.110501901723589</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.246317132720695</v>
+        <v>3.188347183922111</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06930816223163783</v>
+        <v>0.06929705598516245</v>
       </c>
       <c r="C58">
-        <v>708.3280050378264</v>
+        <v>689.7273517387387</v>
       </c>
       <c r="D58">
-        <v>1757.486005037827</v>
+        <v>1757.793351738739</v>
       </c>
       <c r="E58">
-        <v>211.6480000000001</v>
+        <v>230.556</v>
       </c>
       <c r="F58">
-        <v>1058.848</v>
+        <v>1077.756</v>
       </c>
       <c r="G58">
         <v>9.69</v>
@@ -6049,28 +6049,28 @@
         <v>216.4</v>
       </c>
       <c r="M58">
-        <v>67.87215680000001</v>
+        <v>69.08415960000001</v>
       </c>
       <c r="N58">
-        <v>148.5278432</v>
+        <v>147.3158404</v>
       </c>
       <c r="O58">
-        <v>32.67612550400001</v>
+        <v>32.409484888</v>
       </c>
       <c r="P58">
-        <v>115.851717696</v>
+        <v>114.906355512</v>
       </c>
       <c r="Q58">
-        <v>177.251717696</v>
+        <v>176.306355512</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09388473234463141</v>
+        <v>0.09487952554688943</v>
       </c>
       <c r="T58">
-        <v>1.110501901723589</v>
+        <v>1.133476340574814</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.188347183922111</v>
+        <v>3.132411268414706</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06929705598516245</v>
+        <v>0.06928594973868708</v>
       </c>
       <c r="C59">
-        <v>689.7273517387387</v>
+        <v>671.1268059551771</v>
       </c>
       <c r="D59">
-        <v>1757.793351738739</v>
+        <v>1758.100805955177</v>
       </c>
       <c r="E59">
-        <v>230.556</v>
+        <v>249.4640000000002</v>
       </c>
       <c r="F59">
-        <v>1077.756</v>
+        <v>1096.664</v>
       </c>
       <c r="G59">
         <v>9.69</v>
@@ -6131,28 +6131,28 @@
         <v>216.4</v>
       </c>
       <c r="M59">
-        <v>69.08415960000001</v>
+        <v>70.29616240000001</v>
       </c>
       <c r="N59">
-        <v>147.3158404</v>
+        <v>146.1038376</v>
       </c>
       <c r="O59">
-        <v>32.409484888</v>
+        <v>32.142844272</v>
       </c>
       <c r="P59">
-        <v>114.906355512</v>
+        <v>113.960993328</v>
       </c>
       <c r="Q59">
-        <v>176.306355512</v>
+        <v>175.360993328</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09487952554688943</v>
+        <v>0.09592168985401686</v>
       </c>
       <c r="T59">
-        <v>1.133476340574814</v>
+        <v>1.157544800323715</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.132411268414706</v>
+        <v>3.078404177579969</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06928594973868708</v>
+        <v>0.06927484349221172</v>
       </c>
       <c r="C60">
-        <v>671.1268059551774</v>
+        <v>652.5263677435692</v>
       </c>
       <c r="D60">
-        <v>1758.100805955177</v>
+        <v>1758.408367743569</v>
       </c>
       <c r="E60">
-        <v>249.4639999999999</v>
+        <v>268.3719999999998</v>
       </c>
       <c r="F60">
-        <v>1096.664</v>
+        <v>1115.572</v>
       </c>
       <c r="G60">
         <v>9.69</v>
@@ -6213,28 +6213,28 @@
         <v>216.4</v>
       </c>
       <c r="M60">
-        <v>70.2961624</v>
+        <v>71.50816519999999</v>
       </c>
       <c r="N60">
-        <v>146.1038376</v>
+        <v>144.8918348</v>
       </c>
       <c r="O60">
-        <v>32.142844272</v>
+        <v>31.876203656</v>
       </c>
       <c r="P60">
-        <v>113.960993328</v>
+        <v>113.015631144</v>
       </c>
       <c r="Q60">
-        <v>175.360993328</v>
+        <v>174.415631144</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09592168985401686</v>
+        <v>0.09701469144441879</v>
       </c>
       <c r="T60">
-        <v>1.157544800323715</v>
+        <v>1.18278733127988</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.07840417757997</v>
+        <v>3.02622783558709</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06927484349221172</v>
+        <v>0.07291413724573635</v>
       </c>
       <c r="C61">
-        <v>652.5263677435692</v>
+        <v>538.2838977432168</v>
       </c>
       <c r="D61">
-        <v>1758.408367743569</v>
+        <v>1663.073897743217</v>
       </c>
       <c r="E61">
-        <v>268.3719999999998</v>
+        <v>287.28</v>
       </c>
       <c r="F61">
-        <v>1115.572</v>
+        <v>1134.48</v>
       </c>
       <c r="G61">
         <v>9.69</v>
@@ -6295,45 +6295,45 @@
         <v>216.4</v>
       </c>
       <c r="M61">
-        <v>71.50816519999999</v>
+        <v>81.569112</v>
       </c>
       <c r="N61">
-        <v>144.8918348</v>
+        <v>134.830888</v>
       </c>
       <c r="O61">
-        <v>31.876203656</v>
+        <v>29.66279536</v>
       </c>
       <c r="P61">
-        <v>113.015631144</v>
+        <v>105.16809264</v>
       </c>
       <c r="Q61">
-        <v>174.415631144</v>
+        <v>166.56809264</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09701469144441879</v>
+        <v>0.09816234311434086</v>
       </c>
       <c r="T61">
-        <v>1.18278733127988</v>
+        <v>1.209291988783854</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.22</v>
       </c>
       <c r="W61">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.02622783558709</v>
+        <v>2.652965009598241</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07291413724573635</v>
+        <v>0.07296387099926098</v>
       </c>
       <c r="C62">
-        <v>538.2838977432168</v>
+        <v>518.1446250879474</v>
       </c>
       <c r="D62">
-        <v>1663.073897743217</v>
+        <v>1661.842625087947</v>
       </c>
       <c r="E62">
-        <v>287.28</v>
+        <v>306.1879999999999</v>
       </c>
       <c r="F62">
-        <v>1134.48</v>
+        <v>1153.388</v>
       </c>
       <c r="G62">
         <v>9.69</v>
@@ -6377,28 +6377,28 @@
         <v>216.4</v>
       </c>
       <c r="M62">
-        <v>81.569112</v>
+        <v>82.9285972</v>
       </c>
       <c r="N62">
-        <v>134.830888</v>
+        <v>133.4714028</v>
       </c>
       <c r="O62">
-        <v>29.66279536</v>
+        <v>29.363708616</v>
       </c>
       <c r="P62">
-        <v>105.16809264</v>
+        <v>104.107694184</v>
       </c>
       <c r="Q62">
-        <v>166.56809264</v>
+        <v>165.507694184</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09816234311434086</v>
+        <v>0.09936884871605378</v>
       </c>
       <c r="T62">
-        <v>1.209291988783854</v>
+        <v>1.237155859493159</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.652965009598241</v>
+        <v>2.609473779932697</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07296387099926098</v>
+        <v>0.07301360475278561</v>
       </c>
       <c r="C63">
-        <v>518.1446250879474</v>
+        <v>498.0071742528328</v>
       </c>
       <c r="D63">
-        <v>1661.842625087947</v>
+        <v>1660.613174252833</v>
       </c>
       <c r="E63">
-        <v>306.1879999999999</v>
+        <v>325.096</v>
       </c>
       <c r="F63">
-        <v>1153.388</v>
+        <v>1172.296</v>
       </c>
       <c r="G63">
         <v>9.69</v>
@@ -6459,28 +6459,28 @@
         <v>216.4</v>
       </c>
       <c r="M63">
-        <v>82.9285972</v>
+        <v>84.28808240000001</v>
       </c>
       <c r="N63">
-        <v>133.4714028</v>
+        <v>132.1119176</v>
       </c>
       <c r="O63">
-        <v>29.363708616</v>
+        <v>29.064621872</v>
       </c>
       <c r="P63">
-        <v>104.107694184</v>
+        <v>103.047295728</v>
       </c>
       <c r="Q63">
-        <v>165.507694184</v>
+        <v>164.447295728</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09936884871605378</v>
+        <v>0.1006388546125937</v>
       </c>
       <c r="T63">
-        <v>1.237155859493159</v>
+        <v>1.266486249713481</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.609473779932697</v>
+        <v>2.567385493159588</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07301360475278561</v>
+        <v>0.07306333850631025</v>
       </c>
       <c r="C64">
-        <v>498.0071742528328</v>
+        <v>477.8715411974497</v>
       </c>
       <c r="D64">
-        <v>1660.613174252833</v>
+        <v>1659.38554119745</v>
       </c>
       <c r="E64">
-        <v>325.096</v>
+        <v>344.0039999999999</v>
       </c>
       <c r="F64">
-        <v>1172.296</v>
+        <v>1191.204</v>
       </c>
       <c r="G64">
         <v>9.69</v>
@@ -6541,28 +6541,28 @@
         <v>216.4</v>
       </c>
       <c r="M64">
-        <v>84.28808240000001</v>
+        <v>85.6475676</v>
       </c>
       <c r="N64">
-        <v>132.1119176</v>
+        <v>130.7524324</v>
       </c>
       <c r="O64">
-        <v>29.064621872</v>
+        <v>28.765535128</v>
       </c>
       <c r="P64">
-        <v>103.047295728</v>
+        <v>101.986897272</v>
       </c>
       <c r="Q64">
-        <v>164.447295728</v>
+        <v>163.386897272</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1006388546125937</v>
+        <v>0.1019775094765142</v>
       </c>
       <c r="T64">
-        <v>1.266486249713481</v>
+        <v>1.297402066432198</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.567385493159588</v>
+        <v>2.526633342474515</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07306333850631025</v>
+        <v>0.07505995225983489</v>
       </c>
       <c r="C65">
-        <v>477.8715411974497</v>
+        <v>411.134844748871</v>
       </c>
       <c r="D65">
-        <v>1659.38554119745</v>
+        <v>1611.556844748871</v>
       </c>
       <c r="E65">
-        <v>344.0039999999999</v>
+        <v>362.912</v>
       </c>
       <c r="F65">
-        <v>1191.204</v>
+        <v>1210.112</v>
       </c>
       <c r="G65">
         <v>9.69</v>
@@ -6623,45 +6623,45 @@
         <v>216.4</v>
       </c>
       <c r="M65">
-        <v>85.6475676</v>
+        <v>91.72648960000001</v>
       </c>
       <c r="N65">
-        <v>130.7524324</v>
+        <v>124.6735104</v>
       </c>
       <c r="O65">
-        <v>28.765535128</v>
+        <v>27.428172288</v>
       </c>
       <c r="P65">
-        <v>101.986897272</v>
+        <v>97.245338112</v>
       </c>
       <c r="Q65">
-        <v>163.386897272</v>
+        <v>158.645338112</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1019775094765142</v>
+        <v>0.1033905340550969</v>
       </c>
       <c r="T65">
-        <v>1.297402066432198</v>
+        <v>1.330035428524177</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.22</v>
       </c>
       <c r="W65">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.526633342474515</v>
+        <v>2.359187634277459</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07505995225983489</v>
+        <v>0.07514010601335951</v>
       </c>
       <c r="C66">
-        <v>411.134844748871</v>
+        <v>390.3642668449829</v>
       </c>
       <c r="D66">
-        <v>1611.556844748871</v>
+        <v>1609.694266844983</v>
       </c>
       <c r="E66">
-        <v>362.912</v>
+        <v>381.8199999999999</v>
       </c>
       <c r="F66">
-        <v>1210.112</v>
+        <v>1229.02</v>
       </c>
       <c r="G66">
         <v>9.69</v>
@@ -6705,28 +6705,28 @@
         <v>216.4</v>
       </c>
       <c r="M66">
-        <v>91.72648960000001</v>
+        <v>93.159716</v>
       </c>
       <c r="N66">
-        <v>124.6735104</v>
+        <v>123.240284</v>
       </c>
       <c r="O66">
-        <v>27.428172288</v>
+        <v>27.11286248</v>
       </c>
       <c r="P66">
-        <v>97.245338112</v>
+        <v>96.12742152</v>
       </c>
       <c r="Q66">
-        <v>158.645338112</v>
+        <v>157.52742152</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1033905340550969</v>
+        <v>0.1048843028953129</v>
       </c>
       <c r="T66">
-        <v>1.330035428524177</v>
+        <v>1.36453355416427</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.359187634277459</v>
+        <v>2.32289243990396</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07514010601335951</v>
+        <v>0.07522025976688414</v>
       </c>
       <c r="C67">
-        <v>390.3642668449829</v>
+        <v>369.5979893683725</v>
       </c>
       <c r="D67">
-        <v>1609.694266844983</v>
+        <v>1607.835989368373</v>
       </c>
       <c r="E67">
-        <v>381.8199999999999</v>
+        <v>400.7280000000001</v>
       </c>
       <c r="F67">
-        <v>1229.02</v>
+        <v>1247.928</v>
       </c>
       <c r="G67">
         <v>9.69</v>
@@ -6787,28 +6787,28 @@
         <v>216.4</v>
       </c>
       <c r="M67">
-        <v>93.159716</v>
+        <v>94.59294240000001</v>
       </c>
       <c r="N67">
-        <v>123.240284</v>
+        <v>121.8070576</v>
       </c>
       <c r="O67">
-        <v>27.11286248</v>
+        <v>26.797552672</v>
       </c>
       <c r="P67">
-        <v>96.12742152</v>
+        <v>95.009504928</v>
       </c>
       <c r="Q67">
-        <v>157.52742152</v>
+        <v>156.409504928</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1048843028953129</v>
+        <v>0.1064659404908357</v>
       </c>
       <c r="T67">
-        <v>1.36453355416427</v>
+        <v>1.401060981312603</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.32289243990396</v>
+        <v>2.287697099905415</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07522025976688414</v>
+        <v>0.07530041352040878</v>
       </c>
       <c r="C68">
-        <v>369.5979893683725</v>
+        <v>348.8359974426016</v>
       </c>
       <c r="D68">
-        <v>1607.835989368373</v>
+        <v>1605.981997442602</v>
       </c>
       <c r="E68">
-        <v>400.7280000000001</v>
+        <v>419.636</v>
       </c>
       <c r="F68">
-        <v>1247.928</v>
+        <v>1266.836</v>
       </c>
       <c r="G68">
         <v>9.69</v>
@@ -6869,28 +6869,28 @@
         <v>216.4</v>
       </c>
       <c r="M68">
-        <v>94.59294240000001</v>
+        <v>96.02616880000001</v>
       </c>
       <c r="N68">
-        <v>121.8070576</v>
+        <v>120.3738312</v>
       </c>
       <c r="O68">
-        <v>26.797552672</v>
+        <v>26.482242864</v>
       </c>
       <c r="P68">
-        <v>95.009504928</v>
+        <v>93.891588336</v>
       </c>
       <c r="Q68">
-        <v>156.409504928</v>
+        <v>155.291588336</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1064659404908357</v>
+        <v>0.1081434349103296</v>
       </c>
       <c r="T68">
-        <v>1.401060981312603</v>
+        <v>1.439802191924471</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.287697099905415</v>
+        <v>2.253552367071006</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07530041352040878</v>
+        <v>0.0753805672739334</v>
       </c>
       <c r="C69">
-        <v>348.8359974426016</v>
+        <v>328.0782762597705</v>
       </c>
       <c r="D69">
-        <v>1605.981997442602</v>
+        <v>1604.132276259771</v>
       </c>
       <c r="E69">
-        <v>419.636</v>
+        <v>438.5440000000001</v>
       </c>
       <c r="F69">
-        <v>1266.836</v>
+        <v>1285.744</v>
       </c>
       <c r="G69">
         <v>9.69</v>
@@ -6951,28 +6951,28 @@
         <v>216.4</v>
       </c>
       <c r="M69">
-        <v>96.02616880000001</v>
+        <v>97.45939520000002</v>
       </c>
       <c r="N69">
-        <v>120.3738312</v>
+        <v>118.9406048</v>
       </c>
       <c r="O69">
-        <v>26.482242864</v>
+        <v>26.166933056</v>
       </c>
       <c r="P69">
-        <v>93.891588336</v>
+        <v>92.77367174399998</v>
       </c>
       <c r="Q69">
-        <v>155.291588336</v>
+        <v>154.173671744</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1081434349103296</v>
+        <v>0.1099257727310419</v>
       </c>
       <c r="T69">
-        <v>1.439802191924471</v>
+        <v>1.480964728199582</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.253552367071006</v>
+        <v>2.220411891084668</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0753805672739334</v>
+        <v>0.07546072102745803</v>
       </c>
       <c r="C70">
-        <v>328.0782762597705</v>
+        <v>307.3248110801198</v>
       </c>
       <c r="D70">
-        <v>1604.132276259771</v>
+        <v>1602.28681108012</v>
       </c>
       <c r="E70">
-        <v>438.5440000000001</v>
+        <v>457.452</v>
       </c>
       <c r="F70">
-        <v>1285.744</v>
+        <v>1304.652</v>
       </c>
       <c r="G70">
         <v>9.69</v>
@@ -7033,28 +7033,28 @@
         <v>216.4</v>
       </c>
       <c r="M70">
-        <v>97.45939520000002</v>
+        <v>98.89262160000001</v>
       </c>
       <c r="N70">
-        <v>118.9406048</v>
+        <v>117.5073784</v>
       </c>
       <c r="O70">
-        <v>26.166933056</v>
+        <v>25.851623248</v>
       </c>
       <c r="P70">
-        <v>92.77367174399998</v>
+        <v>91.655755152</v>
       </c>
       <c r="Q70">
-        <v>154.173671744</v>
+        <v>153.055755152</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1099257727310419</v>
+        <v>0.1118231000885743</v>
       </c>
       <c r="T70">
-        <v>1.480964728199582</v>
+        <v>1.524782911976312</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.220411891084668</v>
+        <v>2.18823200860518</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07546072102745803</v>
+        <v>0.07554087478098266</v>
       </c>
       <c r="C71">
-        <v>307.3248110801198</v>
+        <v>286.5755872316427</v>
       </c>
       <c r="D71">
-        <v>1602.28681108012</v>
+        <v>1600.445587231643</v>
       </c>
       <c r="E71">
-        <v>457.452</v>
+        <v>476.3600000000001</v>
       </c>
       <c r="F71">
-        <v>1304.652</v>
+        <v>1323.56</v>
       </c>
       <c r="G71">
         <v>9.69</v>
@@ -7115,28 +7115,28 @@
         <v>216.4</v>
       </c>
       <c r="M71">
-        <v>98.89262160000001</v>
+        <v>100.325848</v>
       </c>
       <c r="N71">
-        <v>117.5073784</v>
+        <v>116.074152</v>
       </c>
       <c r="O71">
-        <v>25.851623248</v>
+        <v>25.53631344</v>
       </c>
       <c r="P71">
-        <v>91.655755152</v>
+        <v>90.53783855999998</v>
       </c>
       <c r="Q71">
-        <v>153.055755152</v>
+        <v>151.93783856</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1118231000885743</v>
+        <v>0.1138469159366089</v>
       </c>
       <c r="T71">
-        <v>1.524782911976312</v>
+        <v>1.571522308004824</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.18823200860518</v>
+        <v>2.156971551339391</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07554087478098266</v>
+        <v>0.07562102853450729</v>
       </c>
       <c r="C72">
-        <v>286.5755872316427</v>
+        <v>265.8305901096937</v>
       </c>
       <c r="D72">
-        <v>1600.445587231643</v>
+        <v>1598.608590109694</v>
       </c>
       <c r="E72">
-        <v>476.3600000000001</v>
+        <v>495.268</v>
       </c>
       <c r="F72">
-        <v>1323.56</v>
+        <v>1342.468</v>
       </c>
       <c r="G72">
         <v>9.69</v>
@@ -7197,28 +7197,28 @@
         <v>216.4</v>
       </c>
       <c r="M72">
-        <v>100.325848</v>
+        <v>101.7590744</v>
       </c>
       <c r="N72">
-        <v>116.074152</v>
+        <v>114.6409256</v>
       </c>
       <c r="O72">
-        <v>25.53631344</v>
+        <v>25.221003632</v>
       </c>
       <c r="P72">
-        <v>90.53783855999998</v>
+        <v>89.41992196799998</v>
       </c>
       <c r="Q72">
-        <v>151.93783856</v>
+        <v>150.819921968</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1138469159366089</v>
+        <v>0.1160103052914045</v>
       </c>
       <c r="T72">
-        <v>1.571522308004824</v>
+        <v>1.621485110655993</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.156971551339391</v>
+        <v>2.126591670334611</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07562102853450731</v>
+        <v>0.07570118228803194</v>
       </c>
       <c r="C73">
-        <v>265.8305901096937</v>
+        <v>245.0898051766048</v>
       </c>
       <c r="D73">
-        <v>1598.608590109694</v>
+        <v>1596.775805176605</v>
       </c>
       <c r="E73">
-        <v>495.2679999999998</v>
+        <v>514.1759999999999</v>
       </c>
       <c r="F73">
-        <v>1342.468</v>
+        <v>1361.376</v>
       </c>
       <c r="G73">
         <v>9.69</v>
@@ -7279,28 +7279,28 @@
         <v>216.4</v>
       </c>
       <c r="M73">
-        <v>101.7590744</v>
+        <v>103.1923008</v>
       </c>
       <c r="N73">
-        <v>114.6409256</v>
+        <v>113.2076992</v>
       </c>
       <c r="O73">
-        <v>25.221003632</v>
+        <v>24.905693824</v>
       </c>
       <c r="P73">
-        <v>89.419921968</v>
+        <v>88.302005376</v>
       </c>
       <c r="Q73">
-        <v>150.819921968</v>
+        <v>149.702005376</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1160103052914044</v>
+        <v>0.1183282224572569</v>
       </c>
       <c r="T73">
-        <v>1.621485110655992</v>
+        <v>1.675016684925101</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.126591670334611</v>
+        <v>2.097055674913297</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07570118228803194</v>
+        <v>0.07578133604155657</v>
       </c>
       <c r="C74">
-        <v>245.0898051766048</v>
+        <v>224.3532179612996</v>
       </c>
       <c r="D74">
-        <v>1596.775805176605</v>
+        <v>1594.947217961299</v>
       </c>
       <c r="E74">
-        <v>514.1759999999999</v>
+        <v>533.0839999999998</v>
       </c>
       <c r="F74">
-        <v>1361.376</v>
+        <v>1380.284</v>
       </c>
       <c r="G74">
         <v>9.69</v>
@@ -7361,28 +7361,28 @@
         <v>216.4</v>
       </c>
       <c r="M74">
-        <v>103.1923008</v>
+        <v>104.6255272</v>
       </c>
       <c r="N74">
-        <v>113.2076992</v>
+        <v>111.7744728</v>
       </c>
       <c r="O74">
-        <v>24.905693824</v>
+        <v>24.590384016</v>
       </c>
       <c r="P74">
-        <v>88.302005376</v>
+        <v>87.18408878400001</v>
       </c>
       <c r="Q74">
-        <v>149.702005376</v>
+        <v>148.584088784</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1183282224572569</v>
+        <v>0.1208178371909502</v>
       </c>
       <c r="T74">
-        <v>1.675016684925101</v>
+        <v>1.732513560991922</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.097055674913297</v>
+        <v>2.068328884845992</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07578133604155657</v>
+        <v>0.0758614897950812</v>
       </c>
       <c r="C75">
-        <v>224.3532179612996</v>
+        <v>203.620814058914</v>
       </c>
       <c r="D75">
-        <v>1594.947217961299</v>
+        <v>1593.122814058914</v>
       </c>
       <c r="E75">
-        <v>533.0839999999998</v>
+        <v>551.992</v>
       </c>
       <c r="F75">
-        <v>1380.284</v>
+        <v>1399.192</v>
       </c>
       <c r="G75">
         <v>9.69</v>
@@ -7443,28 +7443,28 @@
         <v>216.4</v>
       </c>
       <c r="M75">
-        <v>104.6255272</v>
+        <v>106.0587536</v>
       </c>
       <c r="N75">
-        <v>111.7744728</v>
+        <v>110.3412464</v>
       </c>
       <c r="O75">
-        <v>24.590384016</v>
+        <v>24.275074208</v>
       </c>
       <c r="P75">
-        <v>87.18408878400001</v>
+        <v>86.06617219200001</v>
       </c>
       <c r="Q75">
-        <v>148.584088784</v>
+        <v>147.466172192</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1208178371909502</v>
+        <v>0.1234989607503122</v>
       </c>
       <c r="T75">
-        <v>1.732513560991922</v>
+        <v>1.794433273679267</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.068328884845992</v>
+        <v>2.040378494510235</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0758614897950812</v>
+        <v>0.07594164354860583</v>
       </c>
       <c r="C76">
-        <v>203.620814058914</v>
+        <v>182.8925791304173</v>
       </c>
       <c r="D76">
-        <v>1593.122814058914</v>
+        <v>1591.302579130417</v>
       </c>
       <c r="E76">
-        <v>551.992</v>
+        <v>570.8999999999999</v>
       </c>
       <c r="F76">
-        <v>1399.192</v>
+        <v>1418.1</v>
       </c>
       <c r="G76">
         <v>9.69</v>
@@ -7525,28 +7525,28 @@
         <v>216.4</v>
       </c>
       <c r="M76">
-        <v>106.0587536</v>
+        <v>107.49198</v>
       </c>
       <c r="N76">
-        <v>110.3412464</v>
+        <v>108.90802</v>
       </c>
       <c r="O76">
-        <v>24.275074208</v>
+        <v>23.9597644</v>
       </c>
       <c r="P76">
-        <v>86.06617219200001</v>
+        <v>84.94825560000001</v>
       </c>
       <c r="Q76">
-        <v>147.466172192</v>
+        <v>146.3482556</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1234989607503122</v>
+        <v>0.1263945741944233</v>
       </c>
       <c r="T76">
-        <v>1.794433273679267</v>
+        <v>1.8613065633816</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.040378494510235</v>
+        <v>2.013173447916766</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07594164354860583</v>
+        <v>0.08443955730213044</v>
       </c>
       <c r="C77">
-        <v>182.8925791304173</v>
+        <v>-7.949442429788178</v>
       </c>
       <c r="D77">
-        <v>1591.302579130417</v>
+        <v>1419.368557570212</v>
       </c>
       <c r="E77">
-        <v>570.8999999999999</v>
+        <v>589.808</v>
       </c>
       <c r="F77">
-        <v>1418.1</v>
+        <v>1437.008</v>
       </c>
       <c r="G77">
         <v>9.69</v>
@@ -7607,45 +7607,45 @@
         <v>216.4</v>
       </c>
       <c r="M77">
-        <v>107.49198</v>
+        <v>129.33072</v>
       </c>
       <c r="N77">
-        <v>108.90802</v>
+        <v>87.06928000000002</v>
       </c>
       <c r="O77">
-        <v>23.9597644</v>
+        <v>19.1552416</v>
       </c>
       <c r="P77">
-        <v>84.94825560000001</v>
+        <v>67.91403840000001</v>
       </c>
       <c r="Q77">
-        <v>146.3482556</v>
+        <v>129.3140384</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1263945741944233</v>
+        <v>0.1295314887588769</v>
       </c>
       <c r="T77">
-        <v>1.8613065633816</v>
+        <v>1.933752627225794</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.22</v>
       </c>
       <c r="W77">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.013173447916766</v>
+        <v>1.673229685878189</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08443955730213044</v>
+        <v>0.08463047105565508</v>
       </c>
       <c r="C78">
-        <v>-7.949442429788178</v>
+        <v>-30.29441622818945</v>
       </c>
       <c r="D78">
-        <v>1419.368557570212</v>
+        <v>1415.93158377181</v>
       </c>
       <c r="E78">
-        <v>589.808</v>
+        <v>608.7159999999999</v>
       </c>
       <c r="F78">
-        <v>1437.008</v>
+        <v>1455.916</v>
       </c>
       <c r="G78">
         <v>9.69</v>
@@ -7689,28 +7689,28 @@
         <v>216.4</v>
       </c>
       <c r="M78">
-        <v>129.33072</v>
+        <v>131.03244</v>
       </c>
       <c r="N78">
-        <v>87.06928000000002</v>
+        <v>85.36756000000003</v>
       </c>
       <c r="O78">
-        <v>19.1552416</v>
+        <v>18.78086320000001</v>
       </c>
       <c r="P78">
-        <v>67.91403840000001</v>
+        <v>66.58669680000003</v>
       </c>
       <c r="Q78">
-        <v>129.3140384</v>
+        <v>127.9866968</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1295314887588769</v>
+        <v>0.1329411785028482</v>
       </c>
       <c r="T78">
-        <v>1.933752627225794</v>
+        <v>2.01249834879557</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.673229685878189</v>
+        <v>1.651499430217434</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08463047105565508</v>
+        <v>0.08482138480917971</v>
       </c>
       <c r="C79">
-        <v>-30.29441622818945</v>
+        <v>-52.62278510254419</v>
       </c>
       <c r="D79">
-        <v>1415.93158377181</v>
+        <v>1412.511214897456</v>
       </c>
       <c r="E79">
-        <v>608.7159999999999</v>
+        <v>627.624</v>
       </c>
       <c r="F79">
-        <v>1455.916</v>
+        <v>1474.824</v>
       </c>
       <c r="G79">
         <v>9.69</v>
@@ -7771,28 +7771,28 @@
         <v>216.4</v>
       </c>
       <c r="M79">
-        <v>131.03244</v>
+        <v>132.73416</v>
       </c>
       <c r="N79">
-        <v>85.36756000000003</v>
+        <v>83.66584</v>
       </c>
       <c r="O79">
-        <v>18.78086320000001</v>
+        <v>18.4064848</v>
       </c>
       <c r="P79">
-        <v>66.58669680000003</v>
+        <v>65.2593552</v>
       </c>
       <c r="Q79">
-        <v>127.9866968</v>
+        <v>126.6593552</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1329411785028482</v>
+        <v>0.136660840041726</v>
       </c>
       <c r="T79">
-        <v>2.01249834879557</v>
+        <v>2.098402772326235</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.651499430217434</v>
+        <v>1.630326360599261</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08482138480917971</v>
+        <v>0.08501229856270434</v>
       </c>
       <c r="C80">
-        <v>-52.62278510254419</v>
+        <v>-74.93466909699964</v>
       </c>
       <c r="D80">
-        <v>1412.511214897456</v>
+        <v>1409.107330903</v>
       </c>
       <c r="E80">
-        <v>627.624</v>
+        <v>646.5319999999999</v>
       </c>
       <c r="F80">
-        <v>1474.824</v>
+        <v>1493.732</v>
       </c>
       <c r="G80">
         <v>9.69</v>
@@ -7853,28 +7853,28 @@
         <v>216.4</v>
       </c>
       <c r="M80">
-        <v>132.73416</v>
+        <v>134.43588</v>
       </c>
       <c r="N80">
-        <v>83.66584</v>
+        <v>81.96412000000001</v>
       </c>
       <c r="O80">
-        <v>18.4064848</v>
+        <v>18.0321064</v>
       </c>
       <c r="P80">
-        <v>65.2593552</v>
+        <v>63.9320136</v>
       </c>
       <c r="Q80">
-        <v>126.6593552</v>
+        <v>125.3320136</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.136660840041726</v>
+        <v>0.1407347550604969</v>
       </c>
       <c r="T80">
-        <v>2.098402772326235</v>
+        <v>2.192488569526487</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.630326360599261</v>
+        <v>1.60968931806003</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08501229856270434</v>
+        <v>0.08520321231622897</v>
       </c>
       <c r="C81">
-        <v>-74.93466909699964</v>
+        <v>-97.23018710135239</v>
       </c>
       <c r="D81">
-        <v>1409.107330903</v>
+        <v>1405.719812898648</v>
       </c>
       <c r="E81">
-        <v>646.5319999999999</v>
+        <v>665.4400000000001</v>
       </c>
       <c r="F81">
-        <v>1493.732</v>
+        <v>1512.64</v>
       </c>
       <c r="G81">
         <v>9.69</v>
@@ -7935,28 +7935,28 @@
         <v>216.4</v>
       </c>
       <c r="M81">
-        <v>134.43588</v>
+        <v>136.1376</v>
       </c>
       <c r="N81">
-        <v>81.96412000000001</v>
+        <v>80.26240000000001</v>
       </c>
       <c r="O81">
-        <v>18.0321064</v>
+        <v>17.657728</v>
       </c>
       <c r="P81">
-        <v>63.9320136</v>
+        <v>62.60467200000001</v>
       </c>
       <c r="Q81">
-        <v>125.3320136</v>
+        <v>124.004672</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1407347550604969</v>
+        <v>0.1452160615811449</v>
       </c>
       <c r="T81">
-        <v>2.192488569526487</v>
+        <v>2.295982946446764</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.60968931806003</v>
+        <v>1.58956820158428</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08520321231622897</v>
+        <v>0.08539412606975361</v>
       </c>
       <c r="C82">
-        <v>-97.23018710135239</v>
+        <v>-119.5094568648865</v>
       </c>
       <c r="D82">
-        <v>1405.719812898648</v>
+        <v>1402.348543135113</v>
       </c>
       <c r="E82">
-        <v>665.4400000000001</v>
+        <v>684.348</v>
       </c>
       <c r="F82">
-        <v>1512.64</v>
+        <v>1531.548</v>
       </c>
       <c r="G82">
         <v>9.69</v>
@@ -8017,28 +8017,28 @@
         <v>216.4</v>
       </c>
       <c r="M82">
-        <v>136.1376</v>
+        <v>137.83932</v>
       </c>
       <c r="N82">
-        <v>80.26240000000001</v>
+        <v>78.56068000000002</v>
       </c>
       <c r="O82">
-        <v>17.657728</v>
+        <v>17.2833496</v>
       </c>
       <c r="P82">
-        <v>62.60467200000001</v>
+        <v>61.27733040000001</v>
       </c>
       <c r="Q82">
-        <v>124.004672</v>
+        <v>122.6773304</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1452160615811449</v>
+        <v>0.1501690845776506</v>
       </c>
       <c r="T82">
-        <v>2.295982946446764</v>
+        <v>2.410371468306018</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.58956820158428</v>
+        <v>1.569943902799289</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08539412606975361</v>
+        <v>0.08558503982327824</v>
       </c>
       <c r="C83">
-        <v>-119.5094568648865</v>
+        <v>-141.7725950100205</v>
       </c>
       <c r="D83">
-        <v>1402.348543135113</v>
+        <v>1398.99340498998</v>
       </c>
       <c r="E83">
-        <v>684.348</v>
+        <v>703.2560000000001</v>
       </c>
       <c r="F83">
-        <v>1531.548</v>
+        <v>1550.456</v>
       </c>
       <c r="G83">
         <v>9.69</v>
@@ -8099,28 +8099,28 @@
         <v>216.4</v>
       </c>
       <c r="M83">
-        <v>137.83932</v>
+        <v>139.54104</v>
       </c>
       <c r="N83">
-        <v>78.56068000000002</v>
+        <v>76.85896</v>
       </c>
       <c r="O83">
-        <v>17.2833496</v>
+        <v>16.9089712</v>
       </c>
       <c r="P83">
-        <v>61.27733040000001</v>
+        <v>59.9499888</v>
       </c>
       <c r="Q83">
-        <v>122.6773304</v>
+        <v>121.3499888</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1501690845776506</v>
+        <v>0.1556724434626569</v>
       </c>
       <c r="T83">
-        <v>2.410371468306018</v>
+        <v>2.537469825927412</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.569943902799289</v>
+        <v>1.550798245448077</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08558503982327824</v>
+        <v>0.08577595357680287</v>
       </c>
       <c r="C84">
-        <v>-141.7725950100205</v>
+        <v>-164.0197170457523</v>
       </c>
       <c r="D84">
-        <v>1398.99340498998</v>
+        <v>1395.654282954248</v>
       </c>
       <c r="E84">
-        <v>703.2560000000001</v>
+        <v>722.164</v>
       </c>
       <c r="F84">
-        <v>1550.456</v>
+        <v>1569.364</v>
       </c>
       <c r="G84">
         <v>9.69</v>
@@ -8181,28 +8181,28 @@
         <v>216.4</v>
       </c>
       <c r="M84">
-        <v>139.54104</v>
+        <v>141.24276</v>
       </c>
       <c r="N84">
-        <v>76.85896</v>
+        <v>75.15724</v>
       </c>
       <c r="O84">
-        <v>16.9089712</v>
+        <v>16.5345928</v>
       </c>
       <c r="P84">
-        <v>59.9499888</v>
+        <v>58.6226472</v>
       </c>
       <c r="Q84">
-        <v>121.3499888</v>
+        <v>120.0226472</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1556724434626569</v>
+        <v>0.1618232563341346</v>
       </c>
       <c r="T84">
-        <v>2.537469825927412</v>
+        <v>2.679520931504263</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.550798245448077</v>
+        <v>1.53211392923786</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08577595357680287</v>
+        <v>0.0859668673303275</v>
       </c>
       <c r="C85">
-        <v>-164.0197170457523</v>
+        <v>-186.2509373809185</v>
       </c>
       <c r="D85">
-        <v>1395.654282954248</v>
+        <v>1392.331062619082</v>
       </c>
       <c r="E85">
-        <v>722.164</v>
+        <v>741.0720000000001</v>
       </c>
       <c r="F85">
-        <v>1569.364</v>
+        <v>1588.272</v>
       </c>
       <c r="G85">
         <v>9.69</v>
@@ -8263,28 +8263,28 @@
         <v>216.4</v>
       </c>
       <c r="M85">
-        <v>141.24276</v>
+        <v>142.94448</v>
       </c>
       <c r="N85">
-        <v>75.15724</v>
+        <v>73.45552000000001</v>
       </c>
       <c r="O85">
-        <v>16.5345928</v>
+        <v>16.1602144</v>
       </c>
       <c r="P85">
-        <v>58.6226472</v>
+        <v>57.29530560000001</v>
       </c>
       <c r="Q85">
-        <v>120.0226472</v>
+        <v>118.6953056</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1618232563341346</v>
+        <v>0.1687429208145469</v>
       </c>
       <c r="T85">
-        <v>2.679520931504263</v>
+        <v>2.839328425278221</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.53211392923786</v>
+        <v>1.513874477699314</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0859668673303275</v>
+        <v>0.1264626166582294</v>
       </c>
       <c r="C86">
-        <v>-186.2509373809182</v>
+        <v>-672.3974914216317</v>
       </c>
       <c r="D86">
-        <v>1392.331062619082</v>
+        <v>925.0925085783681</v>
       </c>
       <c r="E86">
-        <v>741.0719999999999</v>
+        <v>759.9799999999998</v>
       </c>
       <c r="F86">
-        <v>1588.272</v>
+        <v>1607.18</v>
       </c>
       <c r="G86">
         <v>9.69</v>
@@ -8345,45 +8345,45 @@
         <v>216.4</v>
       </c>
       <c r="M86">
-        <v>142.94448</v>
+        <v>235.934024</v>
       </c>
       <c r="N86">
-        <v>73.45552000000001</v>
+        <v>-19.53402399999999</v>
       </c>
       <c r="O86">
-        <v>16.1602144</v>
+        <v>-4.297485279999997</v>
       </c>
       <c r="P86">
-        <v>57.29530560000001</v>
+        <v>-15.23653871999999</v>
       </c>
       <c r="Q86">
-        <v>118.6953056</v>
+        <v>46.16346128000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1687429208145469</v>
+        <v>0.1790758464754959</v>
       </c>
       <c r="T86">
-        <v>2.839328425278219</v>
+        <v>3.077964121835933</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.22</v>
+        <v>0.2017852244998797</v>
       </c>
       <c r="W86">
-        <v>0.0702</v>
+        <v>0.1171779290434177</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.513874477699314</v>
+        <v>0.9172055659085441</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1264626166582294</v>
+        <v>0.1274726166582294</v>
       </c>
       <c r="C87">
-        <v>-672.3974914216317</v>
+        <v>-698.9839400837348</v>
       </c>
       <c r="D87">
-        <v>925.0925085783681</v>
+        <v>917.4140599162652</v>
       </c>
       <c r="E87">
-        <v>759.9799999999998</v>
+        <v>778.8879999999999</v>
       </c>
       <c r="F87">
-        <v>1607.18</v>
+        <v>1626.088</v>
       </c>
       <c r="G87">
         <v>9.69</v>
@@ -8427,37 +8427,37 @@
         <v>216.4</v>
       </c>
       <c r="M87">
-        <v>235.934024</v>
+        <v>238.7097184</v>
       </c>
       <c r="N87">
-        <v>-19.53402399999999</v>
+        <v>-22.30971840000001</v>
       </c>
       <c r="O87">
-        <v>-4.297485279999997</v>
+        <v>-4.908138048000002</v>
       </c>
       <c r="P87">
-        <v>-15.23653871999999</v>
+        <v>-17.40158035200001</v>
       </c>
       <c r="Q87">
-        <v>46.16346128000001</v>
+        <v>43.998419648</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1790758464754959</v>
+        <v>0.1885955497951741</v>
       </c>
       <c r="T87">
-        <v>3.077964121835933</v>
+        <v>3.297818701967071</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2017852244998797</v>
+        <v>0.1994388846801136</v>
       </c>
       <c r="W87">
-        <v>0.1171779290434177</v>
+        <v>0.1175223717289593</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9172055659085441</v>
+        <v>0.9065403849096074</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1274726166582294</v>
+        <v>0.1284826166582294</v>
       </c>
       <c r="C88">
-        <v>-698.9839400837348</v>
+        <v>-725.4439727733017</v>
       </c>
       <c r="D88">
-        <v>917.4140599162652</v>
+        <v>909.8620272266982</v>
       </c>
       <c r="E88">
-        <v>778.8879999999999</v>
+        <v>797.7959999999998</v>
       </c>
       <c r="F88">
-        <v>1626.088</v>
+        <v>1644.996</v>
       </c>
       <c r="G88">
         <v>9.69</v>
@@ -8509,37 +8509,37 @@
         <v>216.4</v>
       </c>
       <c r="M88">
-        <v>238.7097184</v>
+        <v>241.4854128</v>
       </c>
       <c r="N88">
-        <v>-22.30971840000001</v>
+        <v>-25.0854128</v>
       </c>
       <c r="O88">
-        <v>-4.908138048000002</v>
+        <v>-5.518790816</v>
       </c>
       <c r="P88">
-        <v>-17.40158035200001</v>
+        <v>-19.566621984</v>
       </c>
       <c r="Q88">
-        <v>43.998419648</v>
+        <v>41.833378016</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1885955497951741</v>
+        <v>0.1995798228563414</v>
       </c>
       <c r="T88">
-        <v>3.297818701967071</v>
+        <v>3.551497063656845</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1994388846801136</v>
+        <v>0.197146483706779</v>
       </c>
       <c r="W88">
-        <v>0.1175223717289593</v>
+        <v>0.1178588961918449</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9065403849096074</v>
+        <v>0.896120380485359</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1284826166582294</v>
+        <v>0.1294926166582294</v>
       </c>
       <c r="C89">
-        <v>-725.4439727733017</v>
+        <v>-751.7806859202382</v>
       </c>
       <c r="D89">
-        <v>909.8620272266982</v>
+        <v>902.4333140797618</v>
       </c>
       <c r="E89">
-        <v>797.7959999999998</v>
+        <v>816.704</v>
       </c>
       <c r="F89">
-        <v>1644.996</v>
+        <v>1663.904</v>
       </c>
       <c r="G89">
         <v>9.69</v>
@@ -8591,37 +8591,37 @@
         <v>216.4</v>
       </c>
       <c r="M89">
-        <v>241.4854128</v>
+        <v>244.2611072</v>
       </c>
       <c r="N89">
-        <v>-25.0854128</v>
+        <v>-27.86110720000002</v>
       </c>
       <c r="O89">
-        <v>-5.518790816</v>
+        <v>-6.129443584000005</v>
       </c>
       <c r="P89">
-        <v>-19.566621984</v>
+        <v>-21.73166361600002</v>
       </c>
       <c r="Q89">
-        <v>41.833378016</v>
+        <v>39.66833638399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1995798228563414</v>
+        <v>0.2123948080943699</v>
       </c>
       <c r="T89">
-        <v>3.551497063656845</v>
+        <v>3.847455152294917</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.197146483706779</v>
+        <v>0.1949061827555656</v>
       </c>
       <c r="W89">
-        <v>0.1178588961918449</v>
+        <v>0.118187772371483</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.896120380485359</v>
+        <v>0.88593719434348</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1294926166582294</v>
+        <v>0.1305026166582294</v>
       </c>
       <c r="C90">
-        <v>-751.7806859202382</v>
+        <v>-777.9970756482401</v>
       </c>
       <c r="D90">
-        <v>902.4333140797618</v>
+        <v>895.1249243517598</v>
       </c>
       <c r="E90">
-        <v>816.704</v>
+        <v>835.6119999999999</v>
       </c>
       <c r="F90">
-        <v>1663.904</v>
+        <v>1682.812</v>
       </c>
       <c r="G90">
         <v>9.69</v>
@@ -8673,37 +8673,37 @@
         <v>216.4</v>
       </c>
       <c r="M90">
-        <v>244.2611072</v>
+        <v>247.0368016</v>
       </c>
       <c r="N90">
-        <v>-27.86110720000002</v>
+        <v>-30.63680160000001</v>
       </c>
       <c r="O90">
-        <v>-6.129443584000005</v>
+        <v>-6.740096352000003</v>
       </c>
       <c r="P90">
-        <v>-21.73166361600002</v>
+        <v>-23.89670524800001</v>
       </c>
       <c r="Q90">
-        <v>39.66833638399999</v>
+        <v>37.50329475199999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2123948080943699</v>
+        <v>0.2275397906484035</v>
       </c>
       <c r="T90">
-        <v>3.847455152294917</v>
+        <v>4.197223802503546</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1949061827555656</v>
+        <v>0.1927162256459525</v>
       </c>
       <c r="W90">
-        <v>0.118187772371483</v>
+        <v>0.1185092580751742</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.88593719434348</v>
+        <v>0.8759828438452386</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1305026166582294</v>
+        <v>0.1315126166582294</v>
       </c>
       <c r="C91">
-        <v>-777.9970756482401</v>
+        <v>-804.0960418038305</v>
       </c>
       <c r="D91">
-        <v>895.1249243517598</v>
+        <v>887.9339581961694</v>
       </c>
       <c r="E91">
-        <v>835.6119999999999</v>
+        <v>854.52</v>
       </c>
       <c r="F91">
-        <v>1682.812</v>
+        <v>1701.72</v>
       </c>
       <c r="G91">
         <v>9.69</v>
@@ -8755,37 +8755,37 @@
         <v>216.4</v>
       </c>
       <c r="M91">
-        <v>247.0368016</v>
+        <v>249.812496</v>
       </c>
       <c r="N91">
-        <v>-30.63680160000001</v>
+        <v>-33.41249600000003</v>
       </c>
       <c r="O91">
-        <v>-6.740096352000003</v>
+        <v>-7.350749120000008</v>
       </c>
       <c r="P91">
-        <v>-23.89670524800001</v>
+        <v>-26.06174688000003</v>
       </c>
       <c r="Q91">
-        <v>37.50329475199999</v>
+        <v>35.33825311999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2275397906484035</v>
+        <v>0.2457137697132439</v>
       </c>
       <c r="T91">
-        <v>4.197223802503546</v>
+        <v>4.6169461827539</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1927162256459525</v>
+        <v>0.1905749342498863</v>
       </c>
       <c r="W91">
-        <v>0.1185092580751742</v>
+        <v>0.1188235996521167</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8759828438452386</v>
+        <v>0.866249701135847</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1315126166582294</v>
+        <v>0.1325226166582294</v>
       </c>
       <c r="C92">
-        <v>-804.0960418038305</v>
+        <v>-830.0803917927441</v>
       </c>
       <c r="D92">
-        <v>887.9339581961694</v>
+        <v>880.8576082072558</v>
       </c>
       <c r="E92">
-        <v>854.52</v>
+        <v>873.4279999999999</v>
       </c>
       <c r="F92">
-        <v>1701.72</v>
+        <v>1720.628</v>
       </c>
       <c r="G92">
         <v>9.69</v>
@@ -8837,37 +8837,37 @@
         <v>216.4</v>
       </c>
       <c r="M92">
-        <v>249.812496</v>
+        <v>252.5881904</v>
       </c>
       <c r="N92">
-        <v>-33.41249600000003</v>
+        <v>-36.1881904</v>
       </c>
       <c r="O92">
-        <v>-7.350749120000008</v>
+        <v>-7.961401887999999</v>
       </c>
       <c r="P92">
-        <v>-26.06174688000003</v>
+        <v>-28.226788512</v>
       </c>
       <c r="Q92">
-        <v>35.33825311999998</v>
+        <v>33.173211488</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2457137697132439</v>
+        <v>0.2679264107924932</v>
       </c>
       <c r="T92">
-        <v>4.6169461827539</v>
+        <v>5.12994020305989</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1905749342498863</v>
+        <v>0.1884807042031843</v>
       </c>
       <c r="W92">
-        <v>0.1188235996521167</v>
+        <v>0.1191310326229726</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.866249701135847</v>
+        <v>0.8567304736508379</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1325226166582294</v>
+        <v>0.1335326166582294</v>
       </c>
       <c r="C93">
-        <v>-830.0803917927441</v>
+        <v>-855.9528442343161</v>
       </c>
       <c r="D93">
-        <v>880.8576082072558</v>
+        <v>873.8931557656839</v>
       </c>
       <c r="E93">
-        <v>873.4279999999999</v>
+        <v>892.336</v>
       </c>
       <c r="F93">
-        <v>1720.628</v>
+        <v>1739.536</v>
       </c>
       <c r="G93">
         <v>9.69</v>
@@ -8919,37 +8919,37 @@
         <v>216.4</v>
       </c>
       <c r="M93">
-        <v>252.5881904</v>
+        <v>255.3638848</v>
       </c>
       <c r="N93">
-        <v>-36.1881904</v>
+        <v>-38.96388480000002</v>
       </c>
       <c r="O93">
-        <v>-7.961401887999999</v>
+        <v>-8.572054656000004</v>
       </c>
       <c r="P93">
-        <v>-28.226788512</v>
+        <v>-30.39183014400001</v>
       </c>
       <c r="Q93">
-        <v>33.173211488</v>
+        <v>31.00816985599999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2679264107924932</v>
+        <v>0.2956922121415549</v>
       </c>
       <c r="T93">
-        <v>5.12994020305989</v>
+        <v>5.771182728442378</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1884807042031843</v>
+        <v>0.186432000896628</v>
       </c>
       <c r="W93">
-        <v>0.1191310326229726</v>
+        <v>0.119431782268375</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8567304736508379</v>
+        <v>0.8474181858937634</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1335326166582294</v>
+        <v>0.1345426166582294</v>
       </c>
       <c r="C94">
-        <v>-855.9528442343161</v>
+        <v>-881.7160324438744</v>
       </c>
       <c r="D94">
-        <v>873.8931557656839</v>
+        <v>867.0379675561255</v>
       </c>
       <c r="E94">
-        <v>892.336</v>
+        <v>911.2439999999999</v>
       </c>
       <c r="F94">
-        <v>1739.536</v>
+        <v>1758.444</v>
       </c>
       <c r="G94">
         <v>9.69</v>
@@ -9001,37 +9001,37 @@
         <v>216.4</v>
       </c>
       <c r="M94">
-        <v>255.3638848</v>
+        <v>258.1395792</v>
       </c>
       <c r="N94">
-        <v>-38.96388480000002</v>
+        <v>-41.73957920000001</v>
       </c>
       <c r="O94">
-        <v>-8.572054656000004</v>
+        <v>-9.182707424000002</v>
       </c>
       <c r="P94">
-        <v>-30.39183014400001</v>
+        <v>-32.55687177600001</v>
       </c>
       <c r="Q94">
-        <v>31.00816985599999</v>
+        <v>28.84312822399999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2956922121415549</v>
+        <v>0.3313910995903485</v>
       </c>
       <c r="T94">
-        <v>5.771182728442378</v>
+        <v>6.595637403934147</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.186432000896628</v>
+        <v>0.1844273557256965</v>
       </c>
       <c r="W94">
-        <v>0.119431782268375</v>
+        <v>0.1197260641794678</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8474181858937634</v>
+        <v>0.8383061623895294</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1345426166582294</v>
+        <v>0.1355526166582294</v>
       </c>
       <c r="C95">
-        <v>-881.7160324438744</v>
+        <v>-907.3725077525002</v>
       </c>
       <c r="D95">
-        <v>867.0379675561255</v>
+        <v>860.2894922474999</v>
       </c>
       <c r="E95">
-        <v>911.2439999999999</v>
+        <v>930.152</v>
       </c>
       <c r="F95">
-        <v>1758.444</v>
+        <v>1777.352</v>
       </c>
       <c r="G95">
         <v>9.69</v>
@@ -9083,37 +9083,37 @@
         <v>216.4</v>
       </c>
       <c r="M95">
-        <v>258.1395792</v>
+        <v>260.9152736</v>
       </c>
       <c r="N95">
-        <v>-41.73957920000001</v>
+        <v>-44.51527360000003</v>
       </c>
       <c r="O95">
-        <v>-9.182707424000002</v>
+        <v>-9.793360192000007</v>
       </c>
       <c r="P95">
-        <v>-32.55687177600001</v>
+        <v>-34.72191340800002</v>
       </c>
       <c r="Q95">
-        <v>28.84312822399999</v>
+        <v>26.67808659199998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3313910995903485</v>
+        <v>0.3789896161887401</v>
       </c>
       <c r="T95">
-        <v>6.595637403934147</v>
+        <v>7.694910304589841</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1844273557256965</v>
+        <v>0.1824653625796784</v>
       </c>
       <c r="W95">
-        <v>0.1197260641794678</v>
+        <v>0.1200140847733032</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8383061623895294</v>
+        <v>0.829388011725811</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1355526166582294</v>
+        <v>0.1365626166582294</v>
       </c>
       <c r="C96">
-        <v>-907.3725077525002</v>
+        <v>-932.9247426729554</v>
       </c>
       <c r="D96">
-        <v>860.2894922474999</v>
+        <v>853.6452573270445</v>
       </c>
       <c r="E96">
-        <v>930.152</v>
+        <v>949.0599999999999</v>
       </c>
       <c r="F96">
-        <v>1777.352</v>
+        <v>1796.26</v>
       </c>
       <c r="G96">
         <v>9.69</v>
@@ -9165,37 +9165,37 @@
         <v>216.4</v>
       </c>
       <c r="M96">
-        <v>260.9152736</v>
+        <v>263.690968</v>
       </c>
       <c r="N96">
-        <v>-44.51527360000003</v>
+        <v>-47.29096799999999</v>
       </c>
       <c r="O96">
-        <v>-9.793360192000007</v>
+        <v>-10.40401296</v>
       </c>
       <c r="P96">
-        <v>-34.72191340800002</v>
+        <v>-36.88695504</v>
       </c>
       <c r="Q96">
-        <v>26.67808659199998</v>
+        <v>24.51304496</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3789896161887401</v>
+        <v>0.4456275394264882</v>
       </c>
       <c r="T96">
-        <v>7.694910304589841</v>
+        <v>9.233892365507812</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1824653625796784</v>
+        <v>0.1805446745525239</v>
       </c>
       <c r="W96">
-        <v>0.1200140847733032</v>
+        <v>0.1202960417756895</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.829388011725811</v>
+        <v>0.8206576116023815</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1365626166582294</v>
+        <v>0.1375726166582294</v>
       </c>
       <c r="C97">
-        <v>-932.9247426729554</v>
+        <v>-958.3751339200255</v>
       </c>
       <c r="D97">
-        <v>853.6452573270445</v>
+        <v>847.1028660799745</v>
       </c>
       <c r="E97">
-        <v>949.0599999999999</v>
+        <v>967.9680000000001</v>
       </c>
       <c r="F97">
-        <v>1796.26</v>
+        <v>1815.168</v>
       </c>
       <c r="G97">
         <v>9.69</v>
@@ -9247,37 +9247,37 @@
         <v>216.4</v>
       </c>
       <c r="M97">
-        <v>263.690968</v>
+        <v>266.4666624</v>
       </c>
       <c r="N97">
-        <v>-47.29096799999999</v>
+        <v>-50.06666240000001</v>
       </c>
       <c r="O97">
-        <v>-10.40401296</v>
+        <v>-11.014665728</v>
       </c>
       <c r="P97">
-        <v>-36.88695504</v>
+        <v>-39.05199667200001</v>
       </c>
       <c r="Q97">
-        <v>24.51304496</v>
+        <v>22.34800332799999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4456275394264882</v>
+        <v>0.5455844242831104</v>
       </c>
       <c r="T97">
-        <v>9.233892365507812</v>
+        <v>11.54236545688477</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1805446745525239</v>
+        <v>0.1786640008592685</v>
       </c>
       <c r="W97">
-        <v>0.1202960417756895</v>
+        <v>0.1205721246738594</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8206576116023815</v>
+        <v>0.8121090948148566</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1375726166582294</v>
+        <v>0.1385826166582294</v>
       </c>
       <c r="C98">
-        <v>-958.3751339200253</v>
+        <v>-983.7260052930291</v>
       </c>
       <c r="D98">
-        <v>847.1028660799745</v>
+        <v>840.6599947069707</v>
       </c>
       <c r="E98">
-        <v>967.9679999999998</v>
+        <v>986.8759999999997</v>
       </c>
       <c r="F98">
-        <v>1815.168</v>
+        <v>1834.076</v>
       </c>
       <c r="G98">
         <v>9.69</v>
@@ -9329,37 +9329,37 @@
         <v>216.4</v>
       </c>
       <c r="M98">
-        <v>266.4666624</v>
+        <v>269.2423568</v>
       </c>
       <c r="N98">
-        <v>-50.06666240000001</v>
+        <v>-52.84235679999998</v>
       </c>
       <c r="O98">
-        <v>-11.014665728</v>
+        <v>-11.62531849599999</v>
       </c>
       <c r="P98">
-        <v>-39.05199667200001</v>
+        <v>-41.21703830399998</v>
       </c>
       <c r="Q98">
-        <v>22.34800332799999</v>
+        <v>20.18296169600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5455844242831092</v>
+        <v>0.7121792323774788</v>
       </c>
       <c r="T98">
-        <v>11.54236545688474</v>
+        <v>15.38982060917965</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1786640008592685</v>
+        <v>0.1768221039431936</v>
       </c>
       <c r="W98">
-        <v>0.1205721246738594</v>
+        <v>0.1208425151411392</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8121090948148566</v>
+        <v>0.8037368361054252</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1385826166582294</v>
+        <v>0.1936256230994567</v>
       </c>
       <c r="C99">
-        <v>-983.7260052930291</v>
+        <v>-1248.977809862175</v>
       </c>
       <c r="D99">
-        <v>840.6599947069707</v>
+        <v>594.3161901378245</v>
       </c>
       <c r="E99">
-        <v>986.8759999999997</v>
+        <v>1005.784</v>
       </c>
       <c r="F99">
-        <v>1834.076</v>
+        <v>1852.984</v>
       </c>
       <c r="G99">
         <v>9.69</v>
@@ -9411,45 +9411,45 @@
         <v>216.4</v>
       </c>
       <c r="M99">
-        <v>269.2423568</v>
+        <v>372.0791872</v>
       </c>
       <c r="N99">
-        <v>-52.84235679999998</v>
+        <v>-155.6791872</v>
       </c>
       <c r="O99">
-        <v>-11.62531849599999</v>
+        <v>-34.24942118399999</v>
       </c>
       <c r="P99">
-        <v>-41.21703830399998</v>
+        <v>-121.429766016</v>
       </c>
       <c r="Q99">
-        <v>20.18296169600001</v>
+        <v>-60.02976601599998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7121792323774788</v>
+        <v>1.101019170627583</v>
       </c>
       <c r="T99">
-        <v>15.38982060917965</v>
+        <v>24.36995775121439</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1768221039431936</v>
+        <v>0.1279512577907502</v>
       </c>
       <c r="W99">
-        <v>0.1208425151411392</v>
+        <v>0.1751073874356174</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8037368361054252</v>
+        <v>0.5815966263215918</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1936256230994567</v>
+        <v>0.1951756230994567</v>
       </c>
       <c r="C100">
-        <v>-1248.977809862175</v>
+        <v>-1272.749874671023</v>
       </c>
       <c r="D100">
-        <v>594.3161901378245</v>
+        <v>589.4521253289765</v>
       </c>
       <c r="E100">
-        <v>1005.784</v>
+        <v>1024.692</v>
       </c>
       <c r="F100">
-        <v>1852.984</v>
+        <v>1871.892</v>
       </c>
       <c r="G100">
         <v>9.69</v>
@@ -9493,37 +9493,37 @@
         <v>216.4</v>
       </c>
       <c r="M100">
-        <v>372.0791872</v>
+        <v>375.8759136</v>
       </c>
       <c r="N100">
-        <v>-155.6791872</v>
+        <v>-159.4759136</v>
       </c>
       <c r="O100">
-        <v>-34.24942118399999</v>
+        <v>-35.08470099199999</v>
       </c>
       <c r="P100">
-        <v>-121.429766016</v>
+        <v>-124.391212608</v>
       </c>
       <c r="Q100">
-        <v>-60.02976601599998</v>
+        <v>-62.99121260799999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.101019170627583</v>
+        <v>2.156238341255166</v>
       </c>
       <c r="T100">
-        <v>24.36995775121439</v>
+        <v>48.73991550242878</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1279512577907502</v>
+        <v>0.1266588208433689</v>
       </c>
       <c r="W100">
-        <v>0.1751073874356174</v>
+        <v>0.1753669087746515</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5815966263215918</v>
+        <v>0.575721912924404</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1951756230994567</v>
-      </c>
-      <c r="C101">
-        <v>-1272.749874671023</v>
-      </c>
-      <c r="D101">
-        <v>589.4521253289765</v>
-      </c>
-      <c r="E101">
-        <v>1024.692</v>
-      </c>
-      <c r="F101">
-        <v>1871.892</v>
-      </c>
-      <c r="G101">
-        <v>9.69</v>
-      </c>
-      <c r="H101">
-        <v>1043.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>277.8</v>
-      </c>
-      <c r="K101">
-        <v>61.4</v>
-      </c>
-      <c r="L101">
-        <v>216.4</v>
-      </c>
-      <c r="M101">
-        <v>375.8759136</v>
-      </c>
-      <c r="N101">
-        <v>-159.4759136</v>
-      </c>
-      <c r="O101">
-        <v>-35.08470099199999</v>
-      </c>
-      <c r="P101">
-        <v>-124.391212608</v>
-      </c>
-      <c r="Q101">
-        <v>-62.99121260799999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.156238341255166</v>
-      </c>
-      <c r="T101">
-        <v>48.73991550242878</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1266588208433689</v>
-      </c>
-      <c r="W101">
-        <v>0.1753669087746515</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.575721912924404</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
